--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287F6D3B-3F63-47BF-976A-738990663510}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BABEF6E-48F1-4136-A5FA-2B67DDA725D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30855" yWindow="1950" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 19-12-2025" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 19-12-2025'!$A$1:$G$2867</definedName>
+    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 29-01-2026'!$A$1:$G$2867</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -33575,7 +33575,7 @@
         <v>15</v>
       </c>
       <c r="G1370" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1371" spans="1:7" x14ac:dyDescent="0.25">

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BABEF6E-48F1-4136-A5FA-2B67DDA725D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84E61A3-6634-4737-B9C5-5D47B9A2F02A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 29-01-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-02-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 29-01-2026'!$A$1:$G$2867</definedName>
+    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 02-02-2026'!$A$1:$G$2867</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -34242,7 +34242,7 @@
         <v>11</v>
       </c>
       <c r="G1399" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1400" spans="1:7" x14ac:dyDescent="0.25">
@@ -34265,7 +34265,7 @@
         <v>11</v>
       </c>
       <c r="G1400" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1401" spans="1:7" x14ac:dyDescent="0.25">
@@ -34288,7 +34288,7 @@
         <v>11</v>
       </c>
       <c r="G1401" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1402" spans="1:7" x14ac:dyDescent="0.25">
@@ -34311,7 +34311,7 @@
         <v>11</v>
       </c>
       <c r="G1402" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1403" spans="1:7" x14ac:dyDescent="0.25">

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9D78E85-9BC5-43D7-B89C-DE7F595ABAA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A1F51D-6FDB-4A79-AFB9-92A1B9424AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15045" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 10-04-2026" sheetId="1" r:id="rId1"/>
@@ -1379,8 +1379,7 @@
     <t>Den Gode Blanketservice</t>
   </si>
   <si>
-    <t>DGB (0.91_x000D_
-0.91)</t>
+    <t>DGB (0.91)</t>
   </si>
   <si>
     <t>Den Dynamiske Blanket</t>

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A8EE47-3DA6-43E0-AEAA-53143D10C996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31FEF371-0742-4263-823D-8410C8478D6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 01-06-2026'!$A$1:$G$2969</definedName>
+    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 02-06-2026'!$A$1:$G$2969</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1451,7 +1451,7 @@
     <t>OS2korrespondance</t>
   </si>
   <si>
-    <t>OS2</t>
+    <t>Digital Identity</t>
   </si>
   <si>
     <t>Patologi</t>

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BABEF6E-48F1-4136-A5FA-2B67DDA725D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFABE05-30C1-470A-ADD0-335D2F2C6952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B0D5892-AD50-4DF7-84A5-2B0D799D98AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A172A1-790B-49A9-BEE5-01D33A7F6096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="3135" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-06-2026" sheetId="1" r:id="rId1"/>

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDA6358E-9D4E-4588-B761-AD1252EE1C4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B259620D-C9E0-49B1-9147-C2AF2412CB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2304" yWindow="2304" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 25-06-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 30-06-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 25-06-2026'!$A$1:$G$3042</definedName>
+    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 30-06-2026'!$A$1:$G$3042</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -1054,6 +1054,9 @@
     <t>EG Patientsky</t>
   </si>
   <si>
+    <t>Test mangler</t>
+  </si>
+  <si>
     <t>eGraviditet</t>
   </si>
   <si>
@@ -1173,9 +1176,6 @@
   </si>
   <si>
     <t>IAM</t>
-  </si>
-  <si>
-    <t>Test mangler</t>
   </si>
   <si>
     <t>JOSA</t>
@@ -23133,7 +23133,7 @@
         <v>18</v>
       </c>
       <c r="G914" t="s">
-        <v>40</v>
+        <v>343</v>
       </c>
     </row>
     <row r="915" spans="1:7" x14ac:dyDescent="0.3">
@@ -23225,7 +23225,7 @@
         <v>11</v>
       </c>
       <c r="G918" t="s">
-        <v>40</v>
+        <v>343</v>
       </c>
     </row>
     <row r="919" spans="1:7" x14ac:dyDescent="0.3">
@@ -23248,7 +23248,7 @@
         <v>11</v>
       </c>
       <c r="G919" t="s">
-        <v>40</v>
+        <v>343</v>
       </c>
     </row>
     <row r="920" spans="1:7" x14ac:dyDescent="0.3">
@@ -23271,7 +23271,7 @@
         <v>18</v>
       </c>
       <c r="G920" t="s">
-        <v>40</v>
+        <v>343</v>
       </c>
     </row>
     <row r="921" spans="1:7" x14ac:dyDescent="0.3">
@@ -23299,19 +23299,19 @@
     </row>
     <row r="922" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B922" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C922" t="s">
         <v>32</v>
       </c>
       <c r="D922" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E922" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F922" t="s">
         <v>18</v>
@@ -23322,19 +23322,19 @@
     </row>
     <row r="923" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B923" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C923" t="s">
         <v>32</v>
       </c>
       <c r="D923" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E923" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F923" t="s">
         <v>11</v>
@@ -23345,19 +23345,19 @@
     </row>
     <row r="924" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B924" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C924" t="s">
         <v>32</v>
       </c>
       <c r="D924" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E924" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F924" t="s">
         <v>11</v>
@@ -23368,19 +23368,19 @@
     </row>
     <row r="925" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B925" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C925" t="s">
         <v>32</v>
       </c>
       <c r="D925" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E925" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F925" t="s">
         <v>18</v>
@@ -23391,7 +23391,7 @@
     </row>
     <row r="926" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B926" t="s">
         <v>44</v>
@@ -23403,7 +23403,7 @@
         <v>41</v>
       </c>
       <c r="E926" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F926" t="s">
         <v>11</v>
@@ -23414,7 +23414,7 @@
     </row>
     <row r="927" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B927" t="s">
         <v>44</v>
@@ -23423,10 +23423,10 @@
         <v>32</v>
       </c>
       <c r="D927" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E927" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F927" t="s">
         <v>11</v>
@@ -23437,10 +23437,10 @@
     </row>
     <row r="928" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B928" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C928" t="s">
         <v>199</v>
@@ -23460,10 +23460,10 @@
     </row>
     <row r="929" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B929" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C929" t="s">
         <v>199</v>
@@ -23483,10 +23483,10 @@
     </row>
     <row r="930" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B930" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C930" t="s">
         <v>199</v>
@@ -23506,10 +23506,10 @@
     </row>
     <row r="931" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B931" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C931" t="s">
         <v>199</v>
@@ -23529,10 +23529,10 @@
     </row>
     <row r="932" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B932" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C932" t="s">
         <v>199</v>
@@ -23552,10 +23552,10 @@
     </row>
     <row r="933" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B933" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C933" t="s">
         <v>199</v>
@@ -23575,10 +23575,10 @@
     </row>
     <row r="934" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B934" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C934" t="s">
         <v>199</v>
@@ -23598,10 +23598,10 @@
     </row>
     <row r="935" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B935" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C935" t="s">
         <v>199</v>
@@ -23621,10 +23621,10 @@
     </row>
     <row r="936" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B936" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C936" t="s">
         <v>199</v>
@@ -23644,10 +23644,10 @@
     </row>
     <row r="937" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B937" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C937" t="s">
         <v>199</v>
@@ -23667,10 +23667,10 @@
     </row>
     <row r="938" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B938" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C938" t="s">
         <v>199</v>
@@ -23679,7 +23679,7 @@
         <v>196</v>
       </c>
       <c r="E938" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F938" t="s">
         <v>11</v>
@@ -23690,10 +23690,10 @@
     </row>
     <row r="939" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B939" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C939" t="s">
         <v>199</v>
@@ -23713,10 +23713,10 @@
     </row>
     <row r="940" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B940" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C940" t="s">
         <v>199</v>
@@ -23736,10 +23736,10 @@
     </row>
     <row r="941" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B941" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C941" t="s">
         <v>199</v>
@@ -23759,10 +23759,10 @@
     </row>
     <row r="942" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B942" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C942" t="s">
         <v>199</v>
@@ -23782,10 +23782,10 @@
     </row>
     <row r="943" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B943" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C943" t="s">
         <v>199</v>
@@ -23805,10 +23805,10 @@
     </row>
     <row r="944" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B944" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C944" t="s">
         <v>199</v>
@@ -23828,10 +23828,10 @@
     </row>
     <row r="945" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B945" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C945" t="s">
         <v>199</v>
@@ -23851,10 +23851,10 @@
     </row>
     <row r="946" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B946" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C946" t="s">
         <v>199</v>
@@ -23874,10 +23874,10 @@
     </row>
     <row r="947" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B947" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C947" t="s">
         <v>199</v>
@@ -23897,10 +23897,10 @@
     </row>
     <row r="948" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B948" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C948" t="s">
         <v>199</v>
@@ -23920,10 +23920,10 @@
     </row>
     <row r="949" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B949" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C949" t="s">
         <v>199</v>
@@ -23943,10 +23943,10 @@
     </row>
     <row r="950" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B950" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C950" t="s">
         <v>199</v>
@@ -23966,10 +23966,10 @@
     </row>
     <row r="951" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B951" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C951" t="s">
         <v>199</v>
@@ -23989,10 +23989,10 @@
     </row>
     <row r="952" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B952" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C952" t="s">
         <v>199</v>
@@ -24012,10 +24012,10 @@
     </row>
     <row r="953" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B953" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C953" t="s">
         <v>199</v>
@@ -24035,10 +24035,10 @@
     </row>
     <row r="954" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B954" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C954" t="s">
         <v>199</v>
@@ -24058,10 +24058,10 @@
     </row>
     <row r="955" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B955" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C955" t="s">
         <v>199</v>
@@ -24081,10 +24081,10 @@
     </row>
     <row r="956" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B956" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C956" t="s">
         <v>199</v>
@@ -24104,10 +24104,10 @@
     </row>
     <row r="957" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B957" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C957" t="s">
         <v>199</v>
@@ -24127,10 +24127,10 @@
     </row>
     <row r="958" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B958" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C958" t="s">
         <v>199</v>
@@ -24150,10 +24150,10 @@
     </row>
     <row r="959" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B959" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C959" t="s">
         <v>199</v>
@@ -24173,10 +24173,10 @@
     </row>
     <row r="960" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B960" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C960" t="s">
         <v>199</v>
@@ -24196,10 +24196,10 @@
     </row>
     <row r="961" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B961" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C961" t="s">
         <v>199</v>
@@ -24219,10 +24219,10 @@
     </row>
     <row r="962" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B962" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C962" t="s">
         <v>199</v>
@@ -24242,10 +24242,10 @@
     </row>
     <row r="963" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B963" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C963" t="s">
         <v>199</v>
@@ -24265,10 +24265,10 @@
     </row>
     <row r="964" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B964" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C964" t="s">
         <v>199</v>
@@ -24288,10 +24288,10 @@
     </row>
     <row r="965" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B965" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C965" t="s">
         <v>199</v>
@@ -24311,10 +24311,10 @@
     </row>
     <row r="966" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B966" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C966" t="s">
         <v>199</v>
@@ -24334,10 +24334,10 @@
     </row>
     <row r="967" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B967" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C967" t="s">
         <v>199</v>
@@ -24357,10 +24357,10 @@
     </row>
     <row r="968" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B968" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C968" t="s">
         <v>199</v>
@@ -24380,10 +24380,10 @@
     </row>
     <row r="969" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B969" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C969" t="s">
         <v>199</v>
@@ -24403,10 +24403,10 @@
     </row>
     <row r="970" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B970" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C970" t="s">
         <v>199</v>
@@ -24426,10 +24426,10 @@
     </row>
     <row r="971" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B971" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C971" t="s">
         <v>199</v>
@@ -24449,10 +24449,10 @@
     </row>
     <row r="972" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B972" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C972" t="s">
         <v>199</v>
@@ -24472,10 +24472,10 @@
     </row>
     <row r="973" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B973" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C973" t="s">
         <v>199</v>
@@ -24495,10 +24495,10 @@
     </row>
     <row r="974" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B974" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C974" t="s">
         <v>199</v>
@@ -24518,10 +24518,10 @@
     </row>
     <row r="975" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B975" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C975" t="s">
         <v>199</v>
@@ -24541,10 +24541,10 @@
     </row>
     <row r="976" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B976" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C976" t="s">
         <v>199</v>
@@ -24564,10 +24564,10 @@
     </row>
     <row r="977" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B977" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C977" t="s">
         <v>199</v>
@@ -24587,10 +24587,10 @@
     </row>
     <row r="978" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B978" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C978" t="s">
         <v>199</v>
@@ -24610,7 +24610,7 @@
     </row>
     <row r="979" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B979" t="s">
         <v>285</v>
@@ -24633,7 +24633,7 @@
     </row>
     <row r="980" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B980" t="s">
         <v>285</v>
@@ -24656,7 +24656,7 @@
     </row>
     <row r="981" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B981" t="s">
         <v>285</v>
@@ -24679,7 +24679,7 @@
     </row>
     <row r="982" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B982" t="s">
         <v>285</v>
@@ -24702,7 +24702,7 @@
     </row>
     <row r="983" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B983" t="s">
         <v>285</v>
@@ -24725,7 +24725,7 @@
     </row>
     <row r="984" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B984" t="s">
         <v>285</v>
@@ -24748,7 +24748,7 @@
     </row>
     <row r="985" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B985" t="s">
         <v>285</v>
@@ -24771,7 +24771,7 @@
     </row>
     <row r="986" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B986" t="s">
         <v>285</v>
@@ -24794,7 +24794,7 @@
     </row>
     <row r="987" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B987" t="s">
         <v>285</v>
@@ -24817,7 +24817,7 @@
     </row>
     <row r="988" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B988" t="s">
         <v>285</v>
@@ -24840,7 +24840,7 @@
     </row>
     <row r="989" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A989" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B989" t="s">
         <v>285</v>
@@ -24863,7 +24863,7 @@
     </row>
     <row r="990" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B990" t="s">
         <v>285</v>
@@ -24886,7 +24886,7 @@
     </row>
     <row r="991" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B991" t="s">
         <v>285</v>
@@ -24909,7 +24909,7 @@
     </row>
     <row r="992" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B992" t="s">
         <v>285</v>
@@ -24932,7 +24932,7 @@
     </row>
     <row r="993" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B993" t="s">
         <v>285</v>
@@ -24955,7 +24955,7 @@
     </row>
     <row r="994" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B994" t="s">
         <v>285</v>
@@ -24978,7 +24978,7 @@
     </row>
     <row r="995" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A995" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B995" t="s">
         <v>285</v>
@@ -25001,7 +25001,7 @@
     </row>
     <row r="996" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B996" t="s">
         <v>285</v>
@@ -25024,7 +25024,7 @@
     </row>
     <row r="997" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B997" t="s">
         <v>285</v>
@@ -25047,7 +25047,7 @@
     </row>
     <row r="998" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B998" t="s">
         <v>285</v>
@@ -25070,7 +25070,7 @@
     </row>
     <row r="999" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B999" t="s">
         <v>285</v>
@@ -25093,7 +25093,7 @@
     </row>
     <row r="1000" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1000" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1000" t="s">
         <v>285</v>
@@ -25116,7 +25116,7 @@
     </row>
     <row r="1001" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1001" t="s">
         <v>285</v>
@@ -25139,7 +25139,7 @@
     </row>
     <row r="1002" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1002" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1002" t="s">
         <v>285</v>
@@ -25162,7 +25162,7 @@
     </row>
     <row r="1003" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1003" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1003" t="s">
         <v>285</v>
@@ -25185,7 +25185,7 @@
     </row>
     <row r="1004" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1004" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1004" t="s">
         <v>285</v>
@@ -25208,7 +25208,7 @@
     </row>
     <row r="1005" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1005" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1005" t="s">
         <v>285</v>
@@ -25231,7 +25231,7 @@
     </row>
     <row r="1006" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1006" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1006" t="s">
         <v>285</v>
@@ -25254,7 +25254,7 @@
     </row>
     <row r="1007" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1007" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1007" t="s">
         <v>285</v>
@@ -25277,7 +25277,7 @@
     </row>
     <row r="1008" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1008" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1008" t="s">
         <v>285</v>
@@ -25300,7 +25300,7 @@
     </row>
     <row r="1009" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1009" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1009" t="s">
         <v>285</v>
@@ -25323,7 +25323,7 @@
     </row>
     <row r="1010" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1010" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1010" t="s">
         <v>285</v>
@@ -25346,7 +25346,7 @@
     </row>
     <row r="1011" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1011" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1011" t="s">
         <v>285</v>
@@ -25369,7 +25369,7 @@
     </row>
     <row r="1012" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1012" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1012" t="s">
         <v>285</v>
@@ -25392,7 +25392,7 @@
     </row>
     <row r="1013" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1013" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1013" t="s">
         <v>285</v>
@@ -25415,7 +25415,7 @@
     </row>
     <row r="1014" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1014" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B1014" t="s">
         <v>285</v>
@@ -25438,7 +25438,7 @@
     </row>
     <row r="1015" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1015" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1015" t="s">
         <v>285</v>
@@ -25461,7 +25461,7 @@
     </row>
     <row r="1016" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1016" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1016" t="s">
         <v>285</v>
@@ -25484,7 +25484,7 @@
     </row>
     <row r="1017" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1017" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1017" t="s">
         <v>285</v>
@@ -25507,7 +25507,7 @@
     </row>
     <row r="1018" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1018" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1018" t="s">
         <v>285</v>
@@ -25530,7 +25530,7 @@
     </row>
     <row r="1019" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1019" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1019" t="s">
         <v>285</v>
@@ -25553,7 +25553,7 @@
     </row>
     <row r="1020" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1020" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1020" t="s">
         <v>285</v>
@@ -25576,7 +25576,7 @@
     </row>
     <row r="1021" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1021" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1021" t="s">
         <v>285</v>
@@ -25599,7 +25599,7 @@
     </row>
     <row r="1022" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1022" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1022" t="s">
         <v>285</v>
@@ -25622,7 +25622,7 @@
     </row>
     <row r="1023" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1023" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1023" t="s">
         <v>285</v>
@@ -25645,7 +25645,7 @@
     </row>
     <row r="1024" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1024" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1024" t="s">
         <v>285</v>
@@ -25668,7 +25668,7 @@
     </row>
     <row r="1025" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1025" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1025" t="s">
         <v>285</v>
@@ -25691,7 +25691,7 @@
     </row>
     <row r="1026" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1026" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1026" t="s">
         <v>285</v>
@@ -25714,7 +25714,7 @@
     </row>
     <row r="1027" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1027" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B1027" t="s">
         <v>285</v>
@@ -25737,10 +25737,10 @@
     </row>
     <row r="1028" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1028" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1028" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1028" t="s">
         <v>32</v>
@@ -25760,10 +25760,10 @@
     </row>
     <row r="1029" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1029" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1029" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1029" t="s">
         <v>32</v>
@@ -25783,10 +25783,10 @@
     </row>
     <row r="1030" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1030" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1030" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1030" t="s">
         <v>32</v>
@@ -25806,10 +25806,10 @@
     </row>
     <row r="1031" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1031" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1031" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1031" t="s">
         <v>32</v>
@@ -25829,10 +25829,10 @@
     </row>
     <row r="1032" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1032" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1032" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1032" t="s">
         <v>32</v>
@@ -25852,10 +25852,10 @@
     </row>
     <row r="1033" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1033" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1033" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1033" t="s">
         <v>32</v>
@@ -25875,10 +25875,10 @@
     </row>
     <row r="1034" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1034" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1034" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1034" t="s">
         <v>32</v>
@@ -25898,10 +25898,10 @@
     </row>
     <row r="1035" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1035" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1035" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1035" t="s">
         <v>32</v>
@@ -25921,10 +25921,10 @@
     </row>
     <row r="1036" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1036" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1036" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1036" t="s">
         <v>32</v>
@@ -25944,10 +25944,10 @@
     </row>
     <row r="1037" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1037" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1037" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1037" t="s">
         <v>32</v>
@@ -25967,10 +25967,10 @@
     </row>
     <row r="1038" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1038" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1038" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1038" t="s">
         <v>32</v>
@@ -25990,10 +25990,10 @@
     </row>
     <row r="1039" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1039" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1039" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1039" t="s">
         <v>32</v>
@@ -26013,19 +26013,19 @@
     </row>
     <row r="1040" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1040" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1040" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1040" t="s">
         <v>32</v>
       </c>
       <c r="D1040" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E1040" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F1040" t="s">
         <v>11</v>
@@ -26036,10 +26036,10 @@
     </row>
     <row r="1041" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1041" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1041" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1041" t="s">
         <v>32</v>
@@ -26059,10 +26059,10 @@
     </row>
     <row r="1042" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1042" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1042" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1042" t="s">
         <v>32</v>
@@ -26082,10 +26082,10 @@
     </row>
     <row r="1043" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1043" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1043" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1043" t="s">
         <v>32</v>
@@ -26105,10 +26105,10 @@
     </row>
     <row r="1044" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1044" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1044" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1044" t="s">
         <v>32</v>
@@ -26128,10 +26128,10 @@
     </row>
     <row r="1045" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1045" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1045" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1045" t="s">
         <v>32</v>
@@ -26151,10 +26151,10 @@
     </row>
     <row r="1046" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1046" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1046" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1046" t="s">
         <v>32</v>
@@ -26174,10 +26174,10 @@
     </row>
     <row r="1047" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1047" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1047" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1047" t="s">
         <v>32</v>
@@ -26197,10 +26197,10 @@
     </row>
     <row r="1048" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1048" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1048" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1048" t="s">
         <v>32</v>
@@ -26220,10 +26220,10 @@
     </row>
     <row r="1049" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1049" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1049" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1049" t="s">
         <v>32</v>
@@ -26243,10 +26243,10 @@
     </row>
     <row r="1050" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1050" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1050" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C1050" t="s">
         <v>32</v>
@@ -26266,10 +26266,10 @@
     </row>
     <row r="1051" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1051" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1051" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1051" t="s">
         <v>117</v>
@@ -26289,10 +26289,10 @@
     </row>
     <row r="1052" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1052" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1052" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1052" t="s">
         <v>117</v>
@@ -26312,10 +26312,10 @@
     </row>
     <row r="1053" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1053" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1053" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1053" t="s">
         <v>117</v>
@@ -26335,10 +26335,10 @@
     </row>
     <row r="1054" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1054" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1054" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1054" t="s">
         <v>117</v>
@@ -26358,10 +26358,10 @@
     </row>
     <row r="1055" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1055" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1055" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1055" t="s">
         <v>117</v>
@@ -26381,10 +26381,10 @@
     </row>
     <row r="1056" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1056" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1056" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1056" t="s">
         <v>117</v>
@@ -26404,10 +26404,10 @@
     </row>
     <row r="1057" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1057" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1057" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1057" t="s">
         <v>117</v>
@@ -26427,10 +26427,10 @@
     </row>
     <row r="1058" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1058" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1058" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1058" t="s">
         <v>117</v>
@@ -26450,10 +26450,10 @@
     </row>
     <row r="1059" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1059" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1059" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1059" t="s">
         <v>117</v>
@@ -26473,10 +26473,10 @@
     </row>
     <row r="1060" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1060" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1060" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1060" t="s">
         <v>117</v>
@@ -26496,10 +26496,10 @@
     </row>
     <row r="1061" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1061" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1061" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1061" t="s">
         <v>117</v>
@@ -26519,10 +26519,10 @@
     </row>
     <row r="1062" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1062" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1062" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1062" t="s">
         <v>117</v>
@@ -26542,10 +26542,10 @@
     </row>
     <row r="1063" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1063" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B1063" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C1063" t="s">
         <v>117</v>
@@ -26565,7 +26565,7 @@
     </row>
     <row r="1064" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1064" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1064" t="s">
         <v>57</v>
@@ -26588,7 +26588,7 @@
     </row>
     <row r="1065" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1065" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1065" t="s">
         <v>57</v>
@@ -26611,7 +26611,7 @@
     </row>
     <row r="1066" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1066" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1066" t="s">
         <v>57</v>
@@ -26634,7 +26634,7 @@
     </row>
     <row r="1067" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1067" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1067" t="s">
         <v>57</v>
@@ -26657,7 +26657,7 @@
     </row>
     <row r="1068" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1068" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1068" t="s">
         <v>57</v>
@@ -26680,7 +26680,7 @@
     </row>
     <row r="1069" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1069" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1069" t="s">
         <v>57</v>
@@ -26703,7 +26703,7 @@
     </row>
     <row r="1070" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1070" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1070" t="s">
         <v>57</v>
@@ -26726,7 +26726,7 @@
     </row>
     <row r="1071" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1071" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1071" t="s">
         <v>57</v>
@@ -26749,7 +26749,7 @@
     </row>
     <row r="1072" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1072" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1072" t="s">
         <v>57</v>
@@ -26772,7 +26772,7 @@
     </row>
     <row r="1073" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1073" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B1073" t="s">
         <v>57</v>
@@ -26795,10 +26795,10 @@
     </row>
     <row r="1074" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1074" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1074" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1074" t="s">
         <v>128</v>
@@ -26818,10 +26818,10 @@
     </row>
     <row r="1075" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1075" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1075" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1075" t="s">
         <v>128</v>
@@ -26841,10 +26841,10 @@
     </row>
     <row r="1076" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1076" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1076" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1076" t="s">
         <v>128</v>
@@ -26864,10 +26864,10 @@
     </row>
     <row r="1077" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1077" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1077" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1077" t="s">
         <v>128</v>
@@ -26887,10 +26887,10 @@
     </row>
     <row r="1078" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1078" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1078" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1078" t="s">
         <v>128</v>
@@ -26910,10 +26910,10 @@
     </row>
     <row r="1079" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1079" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1079" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1079" t="s">
         <v>128</v>
@@ -26933,10 +26933,10 @@
     </row>
     <row r="1080" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1080" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1080" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1080" t="s">
         <v>128</v>
@@ -26956,10 +26956,10 @@
     </row>
     <row r="1081" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1081" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1081" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1081" t="s">
         <v>128</v>
@@ -26979,10 +26979,10 @@
     </row>
     <row r="1082" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1082" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1082" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1082" t="s">
         <v>128</v>
@@ -27002,10 +27002,10 @@
     </row>
     <row r="1083" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1083" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1083" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1083" t="s">
         <v>128</v>
@@ -27025,10 +27025,10 @@
     </row>
     <row r="1084" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1084" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1084" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1084" t="s">
         <v>128</v>
@@ -27048,10 +27048,10 @@
     </row>
     <row r="1085" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1085" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B1085" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C1085" t="s">
         <v>128</v>
@@ -27071,10 +27071,10 @@
     </row>
     <row r="1086" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1086" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1086" t="s">
         <v>367</v>
-      </c>
-      <c r="B1086" t="s">
-        <v>366</v>
       </c>
       <c r="C1086" t="s">
         <v>230</v>
@@ -27094,10 +27094,10 @@
     </row>
     <row r="1087" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1087" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1087" t="s">
         <v>367</v>
-      </c>
-      <c r="B1087" t="s">
-        <v>366</v>
       </c>
       <c r="C1087" t="s">
         <v>230</v>
@@ -27117,10 +27117,10 @@
     </row>
     <row r="1088" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1088" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1088" t="s">
         <v>367</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>366</v>
       </c>
       <c r="C1088" t="s">
         <v>230</v>
@@ -27140,10 +27140,10 @@
     </row>
     <row r="1089" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1089" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1089" t="s">
         <v>367</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>366</v>
       </c>
       <c r="C1089" t="s">
         <v>230</v>
@@ -27163,10 +27163,10 @@
     </row>
     <row r="1090" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1090" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1090" t="s">
         <v>367</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>366</v>
       </c>
       <c r="C1090" t="s">
         <v>230</v>
@@ -27186,10 +27186,10 @@
     </row>
     <row r="1091" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1091" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1091" t="s">
         <v>367</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>366</v>
       </c>
       <c r="C1091" t="s">
         <v>230</v>
@@ -27209,10 +27209,10 @@
     </row>
     <row r="1092" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1092" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1092" t="s">
         <v>367</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>366</v>
       </c>
       <c r="C1092" t="s">
         <v>230</v>
@@ -27232,10 +27232,10 @@
     </row>
     <row r="1093" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1093" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1093" t="s">
         <v>367</v>
-      </c>
-      <c r="B1093" t="s">
-        <v>366</v>
       </c>
       <c r="C1093" t="s">
         <v>230</v>
@@ -27255,10 +27255,10 @@
     </row>
     <row r="1094" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1094" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1094" t="s">
         <v>367</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>366</v>
       </c>
       <c r="C1094" t="s">
         <v>230</v>
@@ -27278,10 +27278,10 @@
     </row>
     <row r="1095" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1095" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1095" t="s">
         <v>367</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>366</v>
       </c>
       <c r="C1095" t="s">
         <v>230</v>
@@ -27301,10 +27301,10 @@
     </row>
     <row r="1096" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1096" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1096" t="s">
         <v>367</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>366</v>
       </c>
       <c r="C1096" t="s">
         <v>230</v>
@@ -27324,10 +27324,10 @@
     </row>
     <row r="1097" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1097" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1097" t="s">
         <v>367</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>366</v>
       </c>
       <c r="C1097" t="s">
         <v>230</v>
@@ -27347,10 +27347,10 @@
     </row>
     <row r="1098" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1098" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1098" t="s">
         <v>367</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>366</v>
       </c>
       <c r="C1098" t="s">
         <v>230</v>
@@ -27370,10 +27370,10 @@
     </row>
     <row r="1099" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1099" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1099" t="s">
         <v>367</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>366</v>
       </c>
       <c r="C1099" t="s">
         <v>230</v>
@@ -27393,10 +27393,10 @@
     </row>
     <row r="1100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1100" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1100" t="s">
         <v>367</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>366</v>
       </c>
       <c r="C1100" t="s">
         <v>230</v>
@@ -27416,10 +27416,10 @@
     </row>
     <row r="1101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1101" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1101" t="s">
         <v>367</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>366</v>
       </c>
       <c r="C1101" t="s">
         <v>230</v>
@@ -27439,10 +27439,10 @@
     </row>
     <row r="1102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1102" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1102" t="s">
         <v>367</v>
-      </c>
-      <c r="B1102" t="s">
-        <v>366</v>
       </c>
       <c r="C1102" t="s">
         <v>230</v>
@@ -27462,10 +27462,10 @@
     </row>
     <row r="1103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1103" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1103" t="s">
         <v>367</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>366</v>
       </c>
       <c r="C1103" t="s">
         <v>230</v>
@@ -27485,10 +27485,10 @@
     </row>
     <row r="1104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1104" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1104" t="s">
         <v>367</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>366</v>
       </c>
       <c r="C1104" t="s">
         <v>230</v>
@@ -27508,10 +27508,10 @@
     </row>
     <row r="1105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1105" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1105" t="s">
         <v>367</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>366</v>
       </c>
       <c r="C1105" t="s">
         <v>230</v>
@@ -27531,10 +27531,10 @@
     </row>
     <row r="1106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1106" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1106" t="s">
         <v>367</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>366</v>
       </c>
       <c r="C1106" t="s">
         <v>230</v>
@@ -27554,10 +27554,10 @@
     </row>
     <row r="1107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1107" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1107" t="s">
         <v>367</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>366</v>
       </c>
       <c r="C1107" t="s">
         <v>230</v>
@@ -27577,10 +27577,10 @@
     </row>
     <row r="1108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1108" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B1108" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C1108" t="s">
         <v>32</v>
@@ -27600,10 +27600,10 @@
     </row>
     <row r="1109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1109" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B1109" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C1109" t="s">
         <v>32</v>
@@ -27623,10 +27623,10 @@
     </row>
     <row r="1110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1110" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B1110" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C1110" t="s">
         <v>32</v>
@@ -27646,10 +27646,10 @@
     </row>
     <row r="1111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1111" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B1111" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1111" t="s">
         <v>75</v>
@@ -27669,10 +27669,10 @@
     </row>
     <row r="1112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1112" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B1112" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1112" t="s">
         <v>75</v>
@@ -27692,10 +27692,10 @@
     </row>
     <row r="1113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1113" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B1113" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1113" t="s">
         <v>75</v>
@@ -27704,7 +27704,7 @@
         <v>76</v>
       </c>
       <c r="E1113" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F1113" t="s">
         <v>18</v>
@@ -27715,10 +27715,10 @@
     </row>
     <row r="1114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1114" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B1114" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1114" t="s">
         <v>75</v>
@@ -27738,10 +27738,10 @@
     </row>
     <row r="1115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1115" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B1115" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1115" t="s">
         <v>75</v>
@@ -27750,7 +27750,7 @@
         <v>76</v>
       </c>
       <c r="E1115" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F1115" t="s">
         <v>18</v>
@@ -27761,10 +27761,10 @@
     </row>
     <row r="1116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1116" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B1116" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1116" t="s">
         <v>75</v>
@@ -27784,10 +27784,10 @@
     </row>
     <row r="1117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1117" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B1117" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1117" t="s">
         <v>75</v>
@@ -27807,10 +27807,10 @@
     </row>
     <row r="1118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1118" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B1118" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1118" t="s">
         <v>75</v>
@@ -27830,10 +27830,10 @@
     </row>
     <row r="1119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1119" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B1119" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1119" t="s">
         <v>75</v>
@@ -27853,10 +27853,10 @@
     </row>
     <row r="1120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1120" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B1120" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1120" t="s">
         <v>75</v>
@@ -27876,10 +27876,10 @@
     </row>
     <row r="1121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1121" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B1121" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1121" t="s">
         <v>75</v>
@@ -27899,10 +27899,10 @@
     </row>
     <row r="1122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1122" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1122" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C1122" t="s">
         <v>32</v>
@@ -27922,10 +27922,10 @@
     </row>
     <row r="1123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1123" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1123" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C1123" t="s">
         <v>32</v>
@@ -27945,10 +27945,10 @@
     </row>
     <row r="1124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1124" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1124" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C1124" t="s">
         <v>32</v>
@@ -27968,10 +27968,10 @@
     </row>
     <row r="1125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1125" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1125" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C1125" t="s">
         <v>32</v>
@@ -27991,10 +27991,10 @@
     </row>
     <row r="1126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1126" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1126" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C1126" t="s">
         <v>32</v>
@@ -28014,10 +28014,10 @@
     </row>
     <row r="1127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1127" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1127" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C1127" t="s">
         <v>32</v>
@@ -28037,10 +28037,10 @@
     </row>
     <row r="1128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1128" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1128" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C1128" t="s">
         <v>32</v>
@@ -28060,10 +28060,10 @@
     </row>
     <row r="1129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1129" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B1129" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C1129" t="s">
         <v>32</v>
@@ -28083,10 +28083,10 @@
     </row>
     <row r="1130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1130" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1130" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1130" t="s">
         <v>32</v>
@@ -28106,10 +28106,10 @@
     </row>
     <row r="1131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1131" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1131" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1131" t="s">
         <v>32</v>
@@ -28129,10 +28129,10 @@
     </row>
     <row r="1132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1132" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1132" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1132" t="s">
         <v>32</v>
@@ -28152,10 +28152,10 @@
     </row>
     <row r="1133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1133" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1133" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1133" t="s">
         <v>32</v>
@@ -28175,10 +28175,10 @@
     </row>
     <row r="1134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1134" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1134" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1134" t="s">
         <v>32</v>
@@ -28187,7 +28187,7 @@
         <v>192</v>
       </c>
       <c r="E1134" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F1134" t="s">
         <v>18</v>
@@ -28198,10 +28198,10 @@
     </row>
     <row r="1135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1135" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1135" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1135" t="s">
         <v>32</v>
@@ -28210,7 +28210,7 @@
         <v>192</v>
       </c>
       <c r="E1135" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F1135" t="s">
         <v>11</v>
@@ -28221,10 +28221,10 @@
     </row>
     <row r="1136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1136" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1136" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1136" t="s">
         <v>32</v>
@@ -28244,10 +28244,10 @@
     </row>
     <row r="1137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1137" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1137" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1137" t="s">
         <v>32</v>
@@ -28267,10 +28267,10 @@
     </row>
     <row r="1138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1138" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1138" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1138" t="s">
         <v>32</v>
@@ -28290,10 +28290,10 @@
     </row>
     <row r="1139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1139" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1139" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1139" t="s">
         <v>32</v>
@@ -28313,10 +28313,10 @@
     </row>
     <row r="1140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1140" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1140" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1140" t="s">
         <v>32</v>
@@ -28336,10 +28336,10 @@
     </row>
     <row r="1141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1141" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1141" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1141" t="s">
         <v>32</v>
@@ -28348,7 +28348,7 @@
         <v>76</v>
       </c>
       <c r="E1141" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F1141" t="s">
         <v>11</v>
@@ -28359,10 +28359,10 @@
     </row>
     <row r="1142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1142" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1142" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1142" t="s">
         <v>32</v>
@@ -28382,10 +28382,10 @@
     </row>
     <row r="1143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1143" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1143" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1143" t="s">
         <v>32</v>
@@ -28405,10 +28405,10 @@
     </row>
     <row r="1144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1144" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1144" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1144" t="s">
         <v>32</v>
@@ -28428,10 +28428,10 @@
     </row>
     <row r="1145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1145" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1145" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1145" t="s">
         <v>32</v>
@@ -28451,10 +28451,10 @@
     </row>
     <row r="1146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1146" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1146" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1146" t="s">
         <v>32</v>
@@ -28474,10 +28474,10 @@
     </row>
     <row r="1147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1147" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1147" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1147" t="s">
         <v>32</v>
@@ -28497,10 +28497,10 @@
     </row>
     <row r="1148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1148" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1148" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1148" t="s">
         <v>32</v>
@@ -28520,10 +28520,10 @@
     </row>
     <row r="1149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1149" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1149" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1149" t="s">
         <v>32</v>
@@ -28543,10 +28543,10 @@
     </row>
     <row r="1150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1150" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1150" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1150" t="s">
         <v>32</v>
@@ -28566,10 +28566,10 @@
     </row>
     <row r="1151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1151" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1151" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1151" t="s">
         <v>32</v>
@@ -28589,10 +28589,10 @@
     </row>
     <row r="1152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1152" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1152" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C1152" t="s">
         <v>32</v>
@@ -28612,10 +28612,10 @@
     </row>
     <row r="1153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1153" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1153" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1153" t="s">
         <v>32</v>
@@ -28635,10 +28635,10 @@
     </row>
     <row r="1154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1154" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1154" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1154" t="s">
         <v>32</v>
@@ -28658,10 +28658,10 @@
     </row>
     <row r="1155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1155" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1155" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1155" t="s">
         <v>32</v>
@@ -28681,10 +28681,10 @@
     </row>
     <row r="1156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1156" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1156" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1156" t="s">
         <v>32</v>
@@ -28704,10 +28704,10 @@
     </row>
     <row r="1157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1157" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1157" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1157" t="s">
         <v>32</v>
@@ -28727,10 +28727,10 @@
     </row>
     <row r="1158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1158" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1158" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1158" t="s">
         <v>32</v>
@@ -28750,10 +28750,10 @@
     </row>
     <row r="1159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1159" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1159" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1159" t="s">
         <v>32</v>
@@ -28773,10 +28773,10 @@
     </row>
     <row r="1160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1160" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1160" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1160" t="s">
         <v>32</v>
@@ -28796,10 +28796,10 @@
     </row>
     <row r="1161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1161" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1161" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1161" t="s">
         <v>32</v>
@@ -28819,10 +28819,10 @@
     </row>
     <row r="1162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1162" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1162" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1162" t="s">
         <v>32</v>
@@ -28842,10 +28842,10 @@
     </row>
     <row r="1163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1163" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1163" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1163" t="s">
         <v>32</v>
@@ -28865,10 +28865,10 @@
     </row>
     <row r="1164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1164" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1164" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1164" t="s">
         <v>32</v>
@@ -28877,7 +28877,7 @@
         <v>218</v>
       </c>
       <c r="E1164" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F1164" t="s">
         <v>18</v>
@@ -28888,10 +28888,10 @@
     </row>
     <row r="1165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1165" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1165" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1165" t="s">
         <v>32</v>
@@ -28911,10 +28911,10 @@
     </row>
     <row r="1166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1166" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1166" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1166" t="s">
         <v>32</v>
@@ -28934,10 +28934,10 @@
     </row>
     <row r="1167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1167" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1167" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1167" t="s">
         <v>32</v>
@@ -28957,10 +28957,10 @@
     </row>
     <row r="1168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1168" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1168" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1168" t="s">
         <v>32</v>
@@ -28980,10 +28980,10 @@
     </row>
     <row r="1169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1169" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1169" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1169" t="s">
         <v>32</v>
@@ -29003,10 +29003,10 @@
     </row>
     <row r="1170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1170" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1170" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1170" t="s">
         <v>32</v>
@@ -29026,10 +29026,10 @@
     </row>
     <row r="1171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1171" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1171" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1171" t="s">
         <v>32</v>
@@ -29049,10 +29049,10 @@
     </row>
     <row r="1172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1172" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1172" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1172" t="s">
         <v>32</v>
@@ -29072,10 +29072,10 @@
     </row>
     <row r="1173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1173" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1173" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1173" t="s">
         <v>32</v>
@@ -29095,10 +29095,10 @@
     </row>
     <row r="1174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1174" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1174" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1174" t="s">
         <v>32</v>
@@ -29118,10 +29118,10 @@
     </row>
     <row r="1175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1175" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1175" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1175" t="s">
         <v>32</v>
@@ -29141,10 +29141,10 @@
     </row>
     <row r="1176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1176" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1176" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1176" t="s">
         <v>32</v>
@@ -29164,10 +29164,10 @@
     </row>
     <row r="1177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1177" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1177" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1177" t="s">
         <v>32</v>
@@ -29187,10 +29187,10 @@
     </row>
     <row r="1178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1178" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B1178" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C1178" t="s">
         <v>32</v>
@@ -29210,7 +29210,7 @@
     </row>
     <row r="1179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1179" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1179" t="s">
         <v>44</v>
@@ -29233,7 +29233,7 @@
     </row>
     <row r="1180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1180" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1180" t="s">
         <v>44</v>
@@ -29256,7 +29256,7 @@
     </row>
     <row r="1181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1181" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1181" t="s">
         <v>44</v>
@@ -29279,7 +29279,7 @@
     </row>
     <row r="1182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1182" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1182" t="s">
         <v>44</v>
@@ -29302,7 +29302,7 @@
     </row>
     <row r="1183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1183" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1183" t="s">
         <v>44</v>
@@ -29325,7 +29325,7 @@
     </row>
     <row r="1184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1184" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1184" t="s">
         <v>44</v>
@@ -29348,7 +29348,7 @@
     </row>
     <row r="1185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1185" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1185" t="s">
         <v>44</v>
@@ -29371,7 +29371,7 @@
     </row>
     <row r="1186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1186" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1186" t="s">
         <v>44</v>
@@ -29389,12 +29389,12 @@
         <v>18</v>
       </c>
       <c r="G1186" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
     </row>
     <row r="1187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1187" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1187" t="s">
         <v>44</v>
@@ -29417,7 +29417,7 @@
     </row>
     <row r="1188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1188" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1188" t="s">
         <v>44</v>
@@ -29440,7 +29440,7 @@
     </row>
     <row r="1189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1189" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1189" t="s">
         <v>44</v>
@@ -29463,7 +29463,7 @@
     </row>
     <row r="1190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1190" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1190" t="s">
         <v>44</v>
@@ -29486,7 +29486,7 @@
     </row>
     <row r="1191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1191" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1191" t="s">
         <v>44</v>
@@ -29509,7 +29509,7 @@
     </row>
     <row r="1192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1192" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1192" t="s">
         <v>44</v>
@@ -29532,7 +29532,7 @@
     </row>
     <row r="1193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1193" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1193" t="s">
         <v>44</v>
@@ -29555,7 +29555,7 @@
     </row>
     <row r="1194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1194" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1194" t="s">
         <v>44</v>
@@ -29578,7 +29578,7 @@
     </row>
     <row r="1195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1195" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1195" t="s">
         <v>44</v>
@@ -29601,7 +29601,7 @@
     </row>
     <row r="1196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1196" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1196" t="s">
         <v>44</v>
@@ -29624,7 +29624,7 @@
     </row>
     <row r="1197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1197" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1197" t="s">
         <v>44</v>
@@ -29642,12 +29642,12 @@
         <v>11</v>
       </c>
       <c r="G1197" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
     </row>
     <row r="1198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1198" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1198" t="s">
         <v>44</v>
@@ -29670,7 +29670,7 @@
     </row>
     <row r="1199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1199" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1199" t="s">
         <v>44</v>
@@ -29693,7 +29693,7 @@
     </row>
     <row r="1200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1200" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1200" t="s">
         <v>44</v>
@@ -29716,7 +29716,7 @@
     </row>
     <row r="1201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1201" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1201" t="s">
         <v>44</v>
@@ -29734,12 +29734,12 @@
         <v>18</v>
       </c>
       <c r="G1201" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
     </row>
     <row r="1202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1202" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1202" t="s">
         <v>44</v>
@@ -29762,7 +29762,7 @@
     </row>
     <row r="1203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1203" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1203" t="s">
         <v>44</v>
@@ -29780,12 +29780,12 @@
         <v>18</v>
       </c>
       <c r="G1203" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
     </row>
     <row r="1204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1204" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1204" t="s">
         <v>44</v>
@@ -29808,7 +29808,7 @@
     </row>
     <row r="1205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1205" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1205" t="s">
         <v>44</v>
@@ -29826,12 +29826,12 @@
         <v>18</v>
       </c>
       <c r="G1205" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
     </row>
     <row r="1206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1206" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1206" t="s">
         <v>44</v>
@@ -29854,7 +29854,7 @@
     </row>
     <row r="1207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1207" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1207" t="s">
         <v>44</v>
@@ -29877,7 +29877,7 @@
     </row>
     <row r="1208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1208" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1208" t="s">
         <v>44</v>
@@ -29900,7 +29900,7 @@
     </row>
     <row r="1209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1209" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1209" t="s">
         <v>44</v>
@@ -29918,12 +29918,12 @@
         <v>11</v>
       </c>
       <c r="G1209" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
     </row>
     <row r="1210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1210" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1210" t="s">
         <v>44</v>
@@ -29946,7 +29946,7 @@
     </row>
     <row r="1211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1211" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1211" t="s">
         <v>44</v>
@@ -29969,7 +29969,7 @@
     </row>
     <row r="1212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1212" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1212" t="s">
         <v>44</v>
@@ -29992,7 +29992,7 @@
     </row>
     <row r="1213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1213" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1213" t="s">
         <v>44</v>
@@ -30015,7 +30015,7 @@
     </row>
     <row r="1214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1214" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1214" t="s">
         <v>44</v>
@@ -32488,7 +32488,7 @@
         <v>196</v>
       </c>
       <c r="E1321" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F1321" t="s">
         <v>11</v>
@@ -32985,7 +32985,7 @@
         <v>390</v>
       </c>
       <c r="B1343" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1343" t="s">
         <v>75</v>
@@ -33008,7 +33008,7 @@
         <v>390</v>
       </c>
       <c r="B1344" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1344" t="s">
         <v>75</v>
@@ -33031,7 +33031,7 @@
         <v>390</v>
       </c>
       <c r="B1345" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1345" t="s">
         <v>75</v>
@@ -33054,7 +33054,7 @@
         <v>390</v>
       </c>
       <c r="B1346" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1346" t="s">
         <v>75</v>
@@ -33077,7 +33077,7 @@
         <v>390</v>
       </c>
       <c r="B1347" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1347" t="s">
         <v>75</v>
@@ -33100,7 +33100,7 @@
         <v>390</v>
       </c>
       <c r="B1348" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1348" t="s">
         <v>75</v>
@@ -33109,7 +33109,7 @@
         <v>76</v>
       </c>
       <c r="E1348" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F1348" t="s">
         <v>18</v>
@@ -33123,7 +33123,7 @@
         <v>390</v>
       </c>
       <c r="B1349" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1349" t="s">
         <v>75</v>
@@ -33146,7 +33146,7 @@
         <v>390</v>
       </c>
       <c r="B1350" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1350" t="s">
         <v>75</v>
@@ -33169,7 +33169,7 @@
         <v>390</v>
       </c>
       <c r="B1351" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1351" t="s">
         <v>75</v>
@@ -34641,7 +34641,7 @@
         <v>407</v>
       </c>
       <c r="B1415" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1415" t="s">
         <v>75</v>
@@ -34664,7 +34664,7 @@
         <v>407</v>
       </c>
       <c r="B1416" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1416" t="s">
         <v>75</v>
@@ -34687,7 +34687,7 @@
         <v>407</v>
       </c>
       <c r="B1417" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1417" t="s">
         <v>75</v>
@@ -34710,7 +34710,7 @@
         <v>407</v>
       </c>
       <c r="B1418" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1418" t="s">
         <v>75</v>
@@ -34733,7 +34733,7 @@
         <v>407</v>
       </c>
       <c r="B1419" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1419" t="s">
         <v>75</v>
@@ -36504,7 +36504,7 @@
         <v>436</v>
       </c>
       <c r="B1496" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C1496" t="s">
         <v>32</v>
@@ -36527,7 +36527,7 @@
         <v>436</v>
       </c>
       <c r="B1497" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C1497" t="s">
         <v>32</v>
@@ -36550,7 +36550,7 @@
         <v>436</v>
       </c>
       <c r="B1498" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C1498" t="s">
         <v>32</v>
@@ -36573,7 +36573,7 @@
         <v>436</v>
       </c>
       <c r="B1499" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C1499" t="s">
         <v>32</v>
@@ -36596,7 +36596,7 @@
         <v>437</v>
       </c>
       <c r="B1500" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1500" t="s">
         <v>32</v>
@@ -36619,7 +36619,7 @@
         <v>437</v>
       </c>
       <c r="B1501" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1501" t="s">
         <v>32</v>
@@ -36642,7 +36642,7 @@
         <v>437</v>
       </c>
       <c r="B1502" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1502" t="s">
         <v>32</v>
@@ -36665,7 +36665,7 @@
         <v>437</v>
       </c>
       <c r="B1503" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1503" t="s">
         <v>32</v>
@@ -36688,7 +36688,7 @@
         <v>437</v>
       </c>
       <c r="B1504" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1504" t="s">
         <v>32</v>
@@ -36711,7 +36711,7 @@
         <v>437</v>
       </c>
       <c r="B1505" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1505" t="s">
         <v>32</v>
@@ -36734,7 +36734,7 @@
         <v>437</v>
       </c>
       <c r="B1506" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1506" t="s">
         <v>32</v>
@@ -36757,7 +36757,7 @@
         <v>437</v>
       </c>
       <c r="B1507" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1507" t="s">
         <v>32</v>
@@ -36780,7 +36780,7 @@
         <v>437</v>
       </c>
       <c r="B1508" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C1508" t="s">
         <v>32</v>
@@ -39710,7 +39710,7 @@
         <v>41</v>
       </c>
       <c r="E1635" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F1635" t="s">
         <v>11</v>
@@ -39730,10 +39730,10 @@
         <v>32</v>
       </c>
       <c r="D1636" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E1636" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F1636" t="s">
         <v>11</v>
@@ -39753,10 +39753,10 @@
         <v>32</v>
       </c>
       <c r="D1637" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E1637" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F1637" t="s">
         <v>11</v>
@@ -39779,7 +39779,7 @@
         <v>41</v>
       </c>
       <c r="E1638" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F1638" t="s">
         <v>11</v>
@@ -39802,7 +39802,7 @@
         <v>41</v>
       </c>
       <c r="E1639" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F1639" t="s">
         <v>11</v>
@@ -39822,10 +39822,10 @@
         <v>32</v>
       </c>
       <c r="D1640" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E1640" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="F1640" t="s">
         <v>11</v>
@@ -41826,7 +41826,7 @@
         <v>196</v>
       </c>
       <c r="E1727" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F1727" t="s">
         <v>11</v>
@@ -44192,10 +44192,10 @@
         <v>464</v>
       </c>
       <c r="D1830" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E1830" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F1830" t="s">
         <v>11</v>
@@ -44974,10 +44974,10 @@
         <v>297</v>
       </c>
       <c r="D1864" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E1864" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F1864" t="s">
         <v>11</v>
@@ -46055,10 +46055,10 @@
         <v>299</v>
       </c>
       <c r="D1911" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E1911" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F1911" t="s">
         <v>11</v>
@@ -46118,7 +46118,7 @@
         <v>470</v>
       </c>
       <c r="B1914" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1914" t="s">
         <v>75</v>
@@ -46141,7 +46141,7 @@
         <v>470</v>
       </c>
       <c r="B1915" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1915" t="s">
         <v>75</v>
@@ -46164,7 +46164,7 @@
         <v>470</v>
       </c>
       <c r="B1916" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C1916" t="s">
         <v>75</v>
@@ -52035,10 +52035,10 @@
         <v>32</v>
       </c>
       <c r="D2171" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E2171" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F2171" t="s">
         <v>11</v>
@@ -52058,10 +52058,10 @@
         <v>32</v>
       </c>
       <c r="D2172" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E2172" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F2172" t="s">
         <v>18</v>
@@ -52081,10 +52081,10 @@
         <v>32</v>
       </c>
       <c r="D2173" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E2173" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F2173" t="s">
         <v>18</v>
@@ -52104,10 +52104,10 @@
         <v>32</v>
       </c>
       <c r="D2174" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E2174" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F2174" t="s">
         <v>11</v>
@@ -53501,7 +53501,7 @@
         <v>509</v>
       </c>
       <c r="B2235" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2235" t="s">
         <v>32</v>
@@ -53510,7 +53510,7 @@
         <v>41</v>
       </c>
       <c r="E2235" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F2235" t="s">
         <v>18</v>
@@ -53524,7 +53524,7 @@
         <v>509</v>
       </c>
       <c r="B2236" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2236" t="s">
         <v>32</v>
@@ -53547,7 +53547,7 @@
         <v>509</v>
       </c>
       <c r="B2237" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2237" t="s">
         <v>32</v>
@@ -53570,7 +53570,7 @@
         <v>509</v>
       </c>
       <c r="B2238" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2238" t="s">
         <v>32</v>
@@ -53593,7 +53593,7 @@
         <v>509</v>
       </c>
       <c r="B2239" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2239" t="s">
         <v>32</v>
@@ -53616,7 +53616,7 @@
         <v>509</v>
       </c>
       <c r="B2240" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2240" t="s">
         <v>32</v>
@@ -53639,7 +53639,7 @@
         <v>509</v>
       </c>
       <c r="B2241" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2241" t="s">
         <v>32</v>
@@ -53662,7 +53662,7 @@
         <v>509</v>
       </c>
       <c r="B2242" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2242" t="s">
         <v>32</v>
@@ -53685,7 +53685,7 @@
         <v>509</v>
       </c>
       <c r="B2243" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2243" t="s">
         <v>32</v>
@@ -53708,7 +53708,7 @@
         <v>509</v>
       </c>
       <c r="B2244" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2244" t="s">
         <v>32</v>
@@ -53731,7 +53731,7 @@
         <v>512</v>
       </c>
       <c r="B2245" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2245" t="s">
         <v>32</v>
@@ -53754,7 +53754,7 @@
         <v>512</v>
       </c>
       <c r="B2246" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2246" t="s">
         <v>32</v>
@@ -53777,7 +53777,7 @@
         <v>512</v>
       </c>
       <c r="B2247" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2247" t="s">
         <v>32</v>
@@ -53800,7 +53800,7 @@
         <v>512</v>
       </c>
       <c r="B2248" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2248" t="s">
         <v>32</v>
@@ -53823,7 +53823,7 @@
         <v>512</v>
       </c>
       <c r="B2249" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2249" t="s">
         <v>32</v>
@@ -53846,7 +53846,7 @@
         <v>512</v>
       </c>
       <c r="B2250" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2250" t="s">
         <v>32</v>
@@ -53869,7 +53869,7 @@
         <v>512</v>
       </c>
       <c r="B2251" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2251" t="s">
         <v>32</v>
@@ -53892,7 +53892,7 @@
         <v>512</v>
       </c>
       <c r="B2252" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2252" t="s">
         <v>32</v>
@@ -53915,7 +53915,7 @@
         <v>512</v>
       </c>
       <c r="B2253" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2253" t="s">
         <v>32</v>
@@ -53947,7 +53947,7 @@
         <v>41</v>
       </c>
       <c r="E2254" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F2254" t="s">
         <v>18</v>
@@ -54381,10 +54381,10 @@
         <v>299</v>
       </c>
       <c r="D2273" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E2273" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F2273" t="s">
         <v>11</v>
@@ -55186,10 +55186,10 @@
         <v>297</v>
       </c>
       <c r="D2308" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E2308" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F2308" t="s">
         <v>11</v>
@@ -57104,7 +57104,7 @@
         <v>18</v>
       </c>
       <c r="G2391" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2392" spans="1:7" x14ac:dyDescent="0.3">
@@ -57121,7 +57121,7 @@
         <v>41</v>
       </c>
       <c r="E2392" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F2392" t="s">
         <v>18</v>
@@ -57141,7 +57141,7 @@
         <v>32</v>
       </c>
       <c r="D2393" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E2393" t="s">
         <v>530</v>
@@ -59734,7 +59734,7 @@
         <v>548</v>
       </c>
       <c r="B2506" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2506" t="s">
         <v>32</v>
@@ -59757,7 +59757,7 @@
         <v>548</v>
       </c>
       <c r="B2507" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C2507" t="s">
         <v>32</v>
@@ -59780,7 +59780,7 @@
         <v>549</v>
       </c>
       <c r="B2508" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2508" t="s">
         <v>117</v>
@@ -59803,7 +59803,7 @@
         <v>549</v>
       </c>
       <c r="B2509" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2509" t="s">
         <v>117</v>
@@ -59826,7 +59826,7 @@
         <v>549</v>
       </c>
       <c r="B2510" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2510" t="s">
         <v>117</v>
@@ -59849,7 +59849,7 @@
         <v>549</v>
       </c>
       <c r="B2511" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2511" t="s">
         <v>117</v>
@@ -59872,7 +59872,7 @@
         <v>549</v>
       </c>
       <c r="B2512" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2512" t="s">
         <v>117</v>
@@ -59895,7 +59895,7 @@
         <v>549</v>
       </c>
       <c r="B2513" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2513" t="s">
         <v>117</v>
@@ -59918,7 +59918,7 @@
         <v>549</v>
       </c>
       <c r="B2514" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2514" t="s">
         <v>117</v>
@@ -59941,7 +59941,7 @@
         <v>549</v>
       </c>
       <c r="B2515" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2515" t="s">
         <v>117</v>
@@ -59964,7 +59964,7 @@
         <v>549</v>
       </c>
       <c r="B2516" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2516" t="s">
         <v>117</v>
@@ -59987,7 +59987,7 @@
         <v>549</v>
       </c>
       <c r="B2517" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2517" t="s">
         <v>117</v>
@@ -60010,7 +60010,7 @@
         <v>549</v>
       </c>
       <c r="B2518" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2518" t="s">
         <v>117</v>
@@ -60033,7 +60033,7 @@
         <v>549</v>
       </c>
       <c r="B2519" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2519" t="s">
         <v>117</v>
@@ -60056,7 +60056,7 @@
         <v>549</v>
       </c>
       <c r="B2520" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C2520" t="s">
         <v>117</v>
@@ -62822,10 +62822,10 @@
         <v>297</v>
       </c>
       <c r="D2640" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E2640" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="F2640" t="s">
         <v>11</v>
@@ -63630,7 +63630,7 @@
         <v>76</v>
       </c>
       <c r="E2675" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F2675" t="s">
         <v>18</v>
@@ -67839,7 +67839,7 @@
         <v>196</v>
       </c>
       <c r="E2858" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F2858" t="s">
         <v>11</v>
@@ -67862,7 +67862,7 @@
         <v>218</v>
       </c>
       <c r="E2859" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F2859" t="s">
         <v>18</v>

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA19F7B-C792-46D9-B984-B47049905B42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A91EE4-1050-4599-BCCD-799CD8F058D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 01-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 01-07-2026'!$A$1:$G$3038</definedName>
+    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 02-07-2026'!$A$1:$G$3038</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8580A3F6-11EF-48DD-92B6-7F9AFB46694B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217750D6-8757-4A77-947C-BCE46A54E30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 03-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 03-07-2026'!$A$1:$G$3038</definedName>
+    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 09-07-2026'!$A$1:$G$3038</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -37735,7 +37735,7 @@
         <v>18</v>
       </c>
       <c r="G1549" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1550" spans="1:7" x14ac:dyDescent="0.3">
@@ -37781,7 +37781,7 @@
         <v>18</v>
       </c>
       <c r="G1551" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1552" spans="1:7" x14ac:dyDescent="0.3">
@@ -37804,7 +37804,7 @@
         <v>11</v>
       </c>
       <c r="G1552" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1553" spans="1:7" x14ac:dyDescent="0.3">
@@ -37827,7 +37827,7 @@
         <v>18</v>
       </c>
       <c r="G1553" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1554" spans="1:7" x14ac:dyDescent="0.3">
@@ -37965,7 +37965,7 @@
         <v>11</v>
       </c>
       <c r="G1559" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1560" spans="1:7" x14ac:dyDescent="0.3">
@@ -37988,7 +37988,7 @@
         <v>18</v>
       </c>
       <c r="G1560" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1561" spans="1:7" x14ac:dyDescent="0.3">
@@ -38034,7 +38034,7 @@
         <v>11</v>
       </c>
       <c r="G1562" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1563" spans="1:7" x14ac:dyDescent="0.3">
@@ -38057,7 +38057,7 @@
         <v>11</v>
       </c>
       <c r="G1563" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1564" spans="1:7" x14ac:dyDescent="0.3">

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{217750D6-8757-4A77-947C-BCE46A54E30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27619FAE-BFFC-467F-87A7-EFDF20893131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 19-08-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 09-07-2026'!$A$1:$G$3038</definedName>
+    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 19-08-2026'!$A$1:$G$3038</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -62207,7 +62207,7 @@
         <v>11</v>
       </c>
       <c r="G2613" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2614" spans="1:7" x14ac:dyDescent="0.3">

--- a/html/Alle systemer (Samlet liste)_excel.XLSX
+++ b/html/Alle systemer (Samlet liste)_excel.XLSX
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E594F8-D7B5-4FC5-8F54-9DF9AF345006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{400103B0-2F0C-4433-882B-C6B36969EB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14625" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 06-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 06-09-2026'!$A$1:$G$3106</definedName>
+    <definedName name="Alle_systemer__Samlet_liste_">'Opdateret d. 07-09-2026'!$A$1:$G$3107</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21742" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21749" uniqueCount="582">
   <si>
     <t>System</t>
   </si>
@@ -1445,10 +1445,10 @@
     <t>Novax</t>
   </si>
   <si>
-    <t>Share Notes</t>
+    <t>Shared Notes</t>
   </si>
   <si>
-    <t>ECN (1.0)</t>
+    <t>Shared Notes (1.0)</t>
   </si>
   <si>
     <t>NOVAX [Privath.]</t>
@@ -2111,7 +2111,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3106"/>
+  <dimension ref="A1:G3107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -4724,16 +4724,16 @@
         <v>103</v>
       </c>
       <c r="D114" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E114" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F114" t="s">
         <v>11</v>
       </c>
       <c r="G114" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
@@ -4747,10 +4747,10 @@
         <v>103</v>
       </c>
       <c r="D115" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E115" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F115" t="s">
         <v>18</v>
@@ -4931,10 +4931,10 @@
         <v>103</v>
       </c>
       <c r="D123" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E123" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F123" t="s">
         <v>18</v>
@@ -5000,16 +5000,16 @@
         <v>103</v>
       </c>
       <c r="D126" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E126" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F126" t="s">
         <v>11</v>
       </c>
       <c r="G126" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
@@ -5161,10 +5161,10 @@
         <v>117</v>
       </c>
       <c r="D133" t="s">
-        <v>118</v>
+        <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="F133" t="s">
         <v>11</v>
@@ -5184,10 +5184,10 @@
         <v>117</v>
       </c>
       <c r="D134" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E134" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F134" t="s">
         <v>11</v>
@@ -5207,10 +5207,10 @@
         <v>117</v>
       </c>
       <c r="D135" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E135" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F135" t="s">
         <v>11</v>
@@ -5230,10 +5230,10 @@
         <v>117</v>
       </c>
       <c r="D136" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E136" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F136" t="s">
         <v>11</v>
@@ -5253,10 +5253,10 @@
         <v>117</v>
       </c>
       <c r="D137" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="E137" t="s">
-        <v>25</v>
+        <v>124</v>
       </c>
       <c r="F137" t="s">
         <v>11</v>
@@ -5276,10 +5276,10 @@
         <v>117</v>
       </c>
       <c r="D138" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E138" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F138" t="s">
         <v>11</v>
@@ -5322,13 +5322,13 @@
         <v>128</v>
       </c>
       <c r="D140" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E140" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F140" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G140" t="s">
         <v>12</v>
@@ -5345,10 +5345,10 @@
         <v>128</v>
       </c>
       <c r="D141" t="s">
-        <v>129</v>
+        <v>24</v>
       </c>
       <c r="E141" t="s">
-        <v>130</v>
+        <v>25</v>
       </c>
       <c r="F141" t="s">
         <v>18</v>
@@ -5368,10 +5368,10 @@
         <v>128</v>
       </c>
       <c r="D142" t="s">
-        <v>19</v>
+        <v>129</v>
       </c>
       <c r="E142" t="s">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="F142" t="s">
         <v>18</v>
@@ -5391,10 +5391,10 @@
         <v>128</v>
       </c>
       <c r="D143" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E143" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F143" t="s">
         <v>18</v>
@@ -5414,13 +5414,13 @@
         <v>128</v>
       </c>
       <c r="D144" t="s">
-        <v>131</v>
+        <v>13</v>
       </c>
       <c r="E144" t="s">
-        <v>132</v>
+        <v>14</v>
       </c>
       <c r="F144" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G144" t="s">
         <v>12</v>
@@ -5437,10 +5437,10 @@
         <v>128</v>
       </c>
       <c r="D145" t="s">
-        <v>19</v>
+        <v>131</v>
       </c>
       <c r="E145" t="s">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="F145" t="s">
         <v>11</v>
@@ -5460,10 +5460,10 @@
         <v>128</v>
       </c>
       <c r="D146" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="E146" t="s">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="F146" t="s">
         <v>11</v>
@@ -5483,10 +5483,10 @@
         <v>128</v>
       </c>
       <c r="D147" t="s">
-        <v>13</v>
+        <v>131</v>
       </c>
       <c r="E147" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="F147" t="s">
         <v>11</v>
@@ -5506,10 +5506,10 @@
         <v>128</v>
       </c>
       <c r="D148" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E148" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F148" t="s">
         <v>11</v>
@@ -5529,10 +5529,10 @@
         <v>128</v>
       </c>
       <c r="D149" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E149" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F149" t="s">
         <v>11</v>
@@ -21583,13 +21583,13 @@
         <v>149</v>
       </c>
       <c r="D847" t="s">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="E847" t="s">
-        <v>176</v>
+        <v>22</v>
       </c>
       <c r="F847" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G847" t="s">
         <v>42</v>
@@ -21836,13 +21836,13 @@
         <v>149</v>
       </c>
       <c r="D858" t="s">
-        <v>21</v>
+        <v>175</v>
       </c>
       <c r="E858" t="s">
-        <v>22</v>
+        <v>176</v>
       </c>
       <c r="F858" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G858" t="s">
         <v>42</v>
@@ -38419,16 +38419,16 @@
         <v>32</v>
       </c>
       <c r="D1579" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E1579" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F1579" t="s">
         <v>11</v>
       </c>
       <c r="G1579" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1580" spans="1:7" x14ac:dyDescent="0.3">
@@ -38442,16 +38442,16 @@
         <v>32</v>
       </c>
       <c r="D1580" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E1580" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F1580" t="s">
         <v>11</v>
       </c>
       <c r="G1580" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1581" spans="1:7" x14ac:dyDescent="0.3">
@@ -41041,10 +41041,10 @@
         <v>143</v>
       </c>
       <c r="D1693" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E1693" t="s">
-        <v>23</v>
+        <v>112</v>
       </c>
       <c r="F1693" t="s">
         <v>18</v>
@@ -41110,10 +41110,10 @@
         <v>143</v>
       </c>
       <c r="D1696" t="s">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="E1696" t="s">
-        <v>206</v>
+        <v>147</v>
       </c>
       <c r="F1696" t="s">
         <v>18</v>
@@ -41547,16 +41547,16 @@
         <v>143</v>
       </c>
       <c r="D1715" t="s">
-        <v>98</v>
+        <v>21</v>
       </c>
       <c r="E1715" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="F1715" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G1715" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1716" spans="1:7" x14ac:dyDescent="0.3">
@@ -41570,16 +41570,16 @@
         <v>143</v>
       </c>
       <c r="D1716" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E1716" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="F1716" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G1716" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1717" spans="1:7" x14ac:dyDescent="0.3">
@@ -41593,10 +41593,10 @@
         <v>143</v>
       </c>
       <c r="D1717" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="E1717" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="F1717" t="s">
         <v>18</v>
@@ -62293,13 +62293,13 @@
         <v>149</v>
       </c>
       <c r="D2617" t="s">
-        <v>84</v>
+        <v>186</v>
       </c>
       <c r="E2617" t="s">
-        <v>308</v>
+        <v>187</v>
       </c>
       <c r="F2617" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2617" t="s">
         <v>12</v>
@@ -62316,10 +62316,10 @@
         <v>149</v>
       </c>
       <c r="D2618" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E2618" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F2618" t="s">
         <v>557</v>
@@ -62592,13 +62592,13 @@
         <v>149</v>
       </c>
       <c r="D2630" t="s">
-        <v>186</v>
+        <v>84</v>
       </c>
       <c r="E2630" t="s">
-        <v>187</v>
+        <v>308</v>
       </c>
       <c r="F2630" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2630" t="s">
         <v>12</v>
@@ -62621,10 +62621,10 @@
         <v>87</v>
       </c>
       <c r="F2631" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2631" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2632" spans="1:7" x14ac:dyDescent="0.3">
@@ -63236,13 +63236,13 @@
         <v>149</v>
       </c>
       <c r="D2658" t="s">
-        <v>98</v>
+        <v>188</v>
       </c>
       <c r="E2658" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="F2658" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2658" t="s">
         <v>12</v>
@@ -63282,10 +63282,10 @@
         <v>149</v>
       </c>
       <c r="D2660" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E2660" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F2660" t="s">
         <v>557</v>
@@ -63610,10 +63610,10 @@
         <v>87</v>
       </c>
       <c r="F2674" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2674" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2675" spans="1:7" x14ac:dyDescent="0.3">
@@ -63696,13 +63696,13 @@
         <v>149</v>
       </c>
       <c r="D2678" t="s">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="E2678" t="s">
-        <v>189</v>
+        <v>99</v>
       </c>
       <c r="F2678" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2678" t="s">
         <v>12</v>
@@ -63926,13 +63926,13 @@
         <v>298</v>
       </c>
       <c r="D2688" t="s">
-        <v>156</v>
+        <v>243</v>
       </c>
       <c r="E2688" t="s">
-        <v>157</v>
+        <v>244</v>
       </c>
       <c r="F2688" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2688" t="s">
         <v>12</v>
@@ -63949,13 +63949,13 @@
         <v>298</v>
       </c>
       <c r="D2689" t="s">
-        <v>243</v>
+        <v>156</v>
       </c>
       <c r="E2689" t="s">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="F2689" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2689" t="s">
         <v>12</v>
@@ -64501,13 +64501,13 @@
         <v>298</v>
       </c>
       <c r="D2713" t="s">
-        <v>299</v>
+        <v>162</v>
       </c>
       <c r="E2713" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F2713" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2713" t="s">
         <v>12</v>
@@ -64639,13 +64639,13 @@
         <v>298</v>
       </c>
       <c r="D2719" t="s">
-        <v>162</v>
+        <v>299</v>
       </c>
       <c r="E2719" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F2719" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2719" t="s">
         <v>12</v>
@@ -64846,16 +64846,16 @@
         <v>75</v>
       </c>
       <c r="D2728" t="s">
-        <v>9</v>
+        <v>566</v>
       </c>
       <c r="E2728" t="s">
-        <v>10</v>
+        <v>567</v>
       </c>
       <c r="F2728" t="s">
         <v>11</v>
       </c>
       <c r="G2728" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2729" spans="1:7" x14ac:dyDescent="0.3">
@@ -64869,16 +64869,16 @@
         <v>75</v>
       </c>
       <c r="D2729" t="s">
-        <v>566</v>
+        <v>9</v>
       </c>
       <c r="E2729" t="s">
-        <v>567</v>
+        <v>10</v>
       </c>
       <c r="F2729" t="s">
         <v>11</v>
       </c>
       <c r="G2729" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2730" spans="1:7" x14ac:dyDescent="0.3">
@@ -64984,10 +64984,10 @@
         <v>149</v>
       </c>
       <c r="D2734" t="s">
-        <v>98</v>
+        <v>9</v>
       </c>
       <c r="E2734" t="s">
-        <v>99</v>
+        <v>10</v>
       </c>
       <c r="F2734" t="s">
         <v>11</v>
@@ -65007,10 +65007,10 @@
         <v>149</v>
       </c>
       <c r="D2735" t="s">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="E2735" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="F2735" t="s">
         <v>18</v>
@@ -65030,10 +65030,10 @@
         <v>149</v>
       </c>
       <c r="D2736" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="E2736" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="F2736" t="s">
         <v>18</v>
@@ -65053,10 +65053,10 @@
         <v>149</v>
       </c>
       <c r="D2737" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="E2737" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="F2737" t="s">
         <v>18</v>
@@ -65076,10 +65076,10 @@
         <v>149</v>
       </c>
       <c r="D2738" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="E2738" t="s">
-        <v>59</v>
+        <v>161</v>
       </c>
       <c r="F2738" t="s">
         <v>18</v>
@@ -65099,10 +65099,10 @@
         <v>149</v>
       </c>
       <c r="D2739" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E2739" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F2739" t="s">
         <v>18</v>
@@ -65122,10 +65122,10 @@
         <v>149</v>
       </c>
       <c r="D2740" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="E2740" t="s">
-        <v>157</v>
+        <v>124</v>
       </c>
       <c r="F2740" t="s">
         <v>18</v>
@@ -65145,13 +65145,13 @@
         <v>149</v>
       </c>
       <c r="D2741" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E2741" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="F2741" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2741" t="s">
         <v>12</v>
@@ -65168,13 +65168,13 @@
         <v>149</v>
       </c>
       <c r="D2742" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="E2742" t="s">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="F2742" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2742" t="s">
         <v>12</v>
@@ -65260,13 +65260,13 @@
         <v>149</v>
       </c>
       <c r="D2746" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E2746" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="F2746" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2746" t="s">
         <v>12</v>
@@ -65283,10 +65283,10 @@
         <v>149</v>
       </c>
       <c r="D2747" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="E2747" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="F2747" t="s">
         <v>18</v>
@@ -65306,10 +65306,10 @@
         <v>149</v>
       </c>
       <c r="D2748" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="E2748" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="F2748" t="s">
         <v>18</v>
@@ -65329,10 +65329,10 @@
         <v>149</v>
       </c>
       <c r="D2749" t="s">
-        <v>150</v>
+        <v>21</v>
       </c>
       <c r="E2749" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="F2749" t="s">
         <v>18</v>
@@ -65352,10 +65352,10 @@
         <v>149</v>
       </c>
       <c r="D2750" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E2750" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="F2750" t="s">
         <v>18</v>
@@ -65375,10 +65375,10 @@
         <v>149</v>
       </c>
       <c r="D2751" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="E2751" t="s">
-        <v>179</v>
+        <v>25</v>
       </c>
       <c r="F2751" t="s">
         <v>18</v>
@@ -65398,10 +65398,10 @@
         <v>149</v>
       </c>
       <c r="D2752" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="E2752" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="F2752" t="s">
         <v>18</v>
@@ -65421,10 +65421,10 @@
         <v>149</v>
       </c>
       <c r="D2753" t="s">
-        <v>19</v>
+        <v>144</v>
       </c>
       <c r="E2753" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="F2753" t="s">
         <v>18</v>
@@ -65444,10 +65444,10 @@
         <v>149</v>
       </c>
       <c r="D2754" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E2754" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2754" t="s">
         <v>18</v>
@@ -65467,10 +65467,10 @@
         <v>149</v>
       </c>
       <c r="D2755" t="s">
-        <v>180</v>
+        <v>13</v>
       </c>
       <c r="E2755" t="s">
-        <v>181</v>
+        <v>14</v>
       </c>
       <c r="F2755" t="s">
         <v>18</v>
@@ -65490,10 +65490,10 @@
         <v>149</v>
       </c>
       <c r="D2756" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="E2756" t="s">
-        <v>99</v>
+        <v>181</v>
       </c>
       <c r="F2756" t="s">
         <v>18</v>
@@ -65513,13 +65513,13 @@
         <v>149</v>
       </c>
       <c r="D2757" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="E2757" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="F2757" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2757" t="s">
         <v>12</v>
@@ -65536,10 +65536,10 @@
         <v>149</v>
       </c>
       <c r="D2758" t="s">
-        <v>92</v>
+        <v>168</v>
       </c>
       <c r="E2758" t="s">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="F2758" t="s">
         <v>18</v>
@@ -65559,13 +65559,13 @@
         <v>149</v>
       </c>
       <c r="D2759" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="E2759" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="F2759" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2759" t="s">
         <v>12</v>
@@ -65582,13 +65582,13 @@
         <v>149</v>
       </c>
       <c r="D2760" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="E2760" t="s">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="F2760" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2760" t="s">
         <v>12</v>
@@ -65605,13 +65605,13 @@
         <v>149</v>
       </c>
       <c r="D2761" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E2761" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="F2761" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2761" t="s">
         <v>12</v>
@@ -65628,10 +65628,10 @@
         <v>149</v>
       </c>
       <c r="D2762" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E2762" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F2762" t="s">
         <v>18</v>
@@ -65651,13 +65651,13 @@
         <v>149</v>
       </c>
       <c r="D2763" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="E2763" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="F2763" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2763" t="s">
         <v>12</v>
@@ -65674,13 +65674,13 @@
         <v>149</v>
       </c>
       <c r="D2764" t="s">
-        <v>168</v>
+        <v>16</v>
       </c>
       <c r="E2764" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="F2764" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2764" t="s">
         <v>12</v>
@@ -65697,16 +65697,16 @@
         <v>149</v>
       </c>
       <c r="D2765" t="s">
-        <v>49</v>
+        <v>473</v>
       </c>
       <c r="E2765" t="s">
-        <v>50</v>
+        <v>474</v>
       </c>
       <c r="F2765" t="s">
         <v>18</v>
       </c>
       <c r="G2765" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2766" spans="1:7" x14ac:dyDescent="0.3">
@@ -65720,13 +65720,13 @@
         <v>149</v>
       </c>
       <c r="D2766" t="s">
-        <v>164</v>
+        <v>51</v>
       </c>
       <c r="E2766" t="s">
-        <v>165</v>
+        <v>52</v>
       </c>
       <c r="F2766" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2766" t="s">
         <v>12</v>
@@ -65743,13 +65743,13 @@
         <v>149</v>
       </c>
       <c r="D2767" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E2767" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F2767" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2767" t="s">
         <v>12</v>
@@ -65766,10 +65766,10 @@
         <v>149</v>
       </c>
       <c r="D2768" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E2768" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F2768" t="s">
         <v>11</v>
@@ -65789,13 +65789,13 @@
         <v>149</v>
       </c>
       <c r="D2769" t="s">
-        <v>188</v>
+        <v>154</v>
       </c>
       <c r="E2769" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="F2769" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2769" t="s">
         <v>12</v>
@@ -65812,10 +65812,10 @@
         <v>149</v>
       </c>
       <c r="D2770" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="E2770" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="F2770" t="s">
         <v>11</v>
@@ -65835,10 +65835,10 @@
         <v>149</v>
       </c>
       <c r="D2771" t="s">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="E2771" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="F2771" t="s">
         <v>11</v>
@@ -65858,10 +65858,10 @@
         <v>149</v>
       </c>
       <c r="D2772" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="E2772" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="F2772" t="s">
         <v>11</v>
@@ -65881,10 +65881,10 @@
         <v>149</v>
       </c>
       <c r="D2773" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="E2773" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="F2773" t="s">
         <v>11</v>
@@ -65904,10 +65904,10 @@
         <v>149</v>
       </c>
       <c r="D2774" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="E2774" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F2774" t="s">
         <v>11</v>
@@ -65927,10 +65927,10 @@
         <v>149</v>
       </c>
       <c r="D2775" t="s">
-        <v>192</v>
+        <v>76</v>
       </c>
       <c r="E2775" t="s">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="F2775" t="s">
         <v>11</v>
@@ -65950,10 +65950,10 @@
         <v>149</v>
       </c>
       <c r="D2776" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E2776" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="F2776" t="s">
         <v>11</v>
@@ -65973,13 +65973,13 @@
         <v>149</v>
       </c>
       <c r="D2777" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="E2777" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
       <c r="F2777" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2777" t="s">
         <v>12</v>
@@ -65996,10 +65996,10 @@
         <v>149</v>
       </c>
       <c r="D2778" t="s">
-        <v>166</v>
+        <v>33</v>
       </c>
       <c r="E2778" t="s">
-        <v>179</v>
+        <v>34</v>
       </c>
       <c r="F2778" t="s">
         <v>11</v>
@@ -66019,10 +66019,10 @@
         <v>149</v>
       </c>
       <c r="D2779" t="s">
-        <v>194</v>
+        <v>129</v>
       </c>
       <c r="E2779" t="s">
-        <v>195</v>
+        <v>130</v>
       </c>
       <c r="F2779" t="s">
         <v>11</v>
@@ -66042,10 +66042,10 @@
         <v>149</v>
       </c>
       <c r="D2780" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E2780" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F2780" t="s">
         <v>11</v>
@@ -66065,10 +66065,10 @@
         <v>149</v>
       </c>
       <c r="D2781" t="s">
-        <v>190</v>
+        <v>154</v>
       </c>
       <c r="E2781" t="s">
-        <v>191</v>
+        <v>155</v>
       </c>
       <c r="F2781" t="s">
         <v>11</v>
@@ -66088,10 +66088,10 @@
         <v>149</v>
       </c>
       <c r="D2782" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="E2782" t="s">
-        <v>130</v>
+        <v>193</v>
       </c>
       <c r="F2782" t="s">
         <v>11</v>
@@ -66111,10 +66111,10 @@
         <v>149</v>
       </c>
       <c r="D2783" t="s">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="E2783" t="s">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="F2783" t="s">
         <v>11</v>
@@ -66263,19 +66263,19 @@
     </row>
     <row r="2790" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2790" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B2790" t="s">
         <v>142</v>
       </c>
       <c r="C2790" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="D2790" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="E2790" t="s">
-        <v>99</v>
+        <v>170</v>
       </c>
       <c r="F2790" t="s">
         <v>11</v>
@@ -66295,10 +66295,10 @@
         <v>199</v>
       </c>
       <c r="D2791" t="s">
-        <v>173</v>
+        <v>98</v>
       </c>
       <c r="E2791" t="s">
-        <v>207</v>
+        <v>99</v>
       </c>
       <c r="F2791" t="s">
         <v>11</v>
@@ -66318,10 +66318,10 @@
         <v>199</v>
       </c>
       <c r="D2792" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E2792" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F2792" t="s">
         <v>11</v>
@@ -66341,10 +66341,10 @@
         <v>199</v>
       </c>
       <c r="D2793" t="s">
-        <v>106</v>
+        <v>182</v>
       </c>
       <c r="E2793" t="s">
-        <v>146</v>
+        <v>206</v>
       </c>
       <c r="F2793" t="s">
         <v>11</v>
@@ -66364,10 +66364,10 @@
         <v>199</v>
       </c>
       <c r="D2794" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="E2794" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F2794" t="s">
         <v>11</v>
@@ -66387,10 +66387,10 @@
         <v>199</v>
       </c>
       <c r="D2795" t="s">
-        <v>182</v>
+        <v>144</v>
       </c>
       <c r="E2795" t="s">
-        <v>183</v>
+        <v>147</v>
       </c>
       <c r="F2795" t="s">
         <v>11</v>
@@ -66410,16 +66410,16 @@
         <v>199</v>
       </c>
       <c r="D2796" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="E2796" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="F2796" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2796" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2797" spans="1:7" x14ac:dyDescent="0.3">
@@ -66433,16 +66433,16 @@
         <v>199</v>
       </c>
       <c r="D2797" t="s">
-        <v>13</v>
+        <v>144</v>
       </c>
       <c r="E2797" t="s">
-        <v>14</v>
+        <v>145</v>
       </c>
       <c r="F2797" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2797" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2798" spans="1:7" x14ac:dyDescent="0.3">
@@ -66456,16 +66456,16 @@
         <v>199</v>
       </c>
       <c r="D2798" t="s">
-        <v>100</v>
+        <v>13</v>
       </c>
       <c r="E2798" t="s">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="F2798" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2798" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2799" spans="1:7" x14ac:dyDescent="0.3">
@@ -66479,10 +66479,10 @@
         <v>199</v>
       </c>
       <c r="D2799" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E2799" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F2799" t="s">
         <v>18</v>
@@ -66502,16 +66502,16 @@
         <v>199</v>
       </c>
       <c r="D2800" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="E2800" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="F2800" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2800" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2801" spans="1:7" x14ac:dyDescent="0.3">
@@ -66525,10 +66525,10 @@
         <v>199</v>
       </c>
       <c r="D2801" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="E2801" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="F2801" t="s">
         <v>11</v>
@@ -66548,10 +66548,10 @@
         <v>199</v>
       </c>
       <c r="D2802" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="E2802" t="s">
-        <v>167</v>
+        <v>205</v>
       </c>
       <c r="F2802" t="s">
         <v>11</v>
@@ -66574,7 +66574,7 @@
         <v>166</v>
       </c>
       <c r="E2803" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="F2803" t="s">
         <v>11</v>
@@ -66594,10 +66594,10 @@
         <v>199</v>
       </c>
       <c r="D2804" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="E2804" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="F2804" t="s">
         <v>11</v>
@@ -66617,10 +66617,10 @@
         <v>199</v>
       </c>
       <c r="D2805" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E2805" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="F2805" t="s">
         <v>11</v>
@@ -66640,10 +66640,10 @@
         <v>199</v>
       </c>
       <c r="D2806" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E2806" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F2806" t="s">
         <v>11</v>
@@ -66663,10 +66663,10 @@
         <v>199</v>
       </c>
       <c r="D2807" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E2807" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F2807" t="s">
         <v>11</v>
@@ -66686,10 +66686,10 @@
         <v>199</v>
       </c>
       <c r="D2808" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="E2808" t="s">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="F2808" t="s">
         <v>11</v>
@@ -66709,13 +66709,13 @@
         <v>199</v>
       </c>
       <c r="D2809" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="E2809" t="s">
-        <v>25</v>
+        <v>208</v>
       </c>
       <c r="F2809" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2809" t="s">
         <v>12</v>
@@ -66732,10 +66732,10 @@
         <v>199</v>
       </c>
       <c r="D2810" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="E2810" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F2810" t="s">
         <v>18</v>
@@ -66755,13 +66755,13 @@
         <v>199</v>
       </c>
       <c r="D2811" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="E2811" t="s">
-        <v>130</v>
+        <v>64</v>
       </c>
       <c r="F2811" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2811" t="s">
         <v>12</v>
@@ -66778,10 +66778,10 @@
         <v>199</v>
       </c>
       <c r="D2812" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="E2812" t="s">
-        <v>202</v>
+        <v>130</v>
       </c>
       <c r="F2812" t="s">
         <v>11</v>
@@ -66801,10 +66801,10 @@
         <v>199</v>
       </c>
       <c r="D2813" t="s">
-        <v>175</v>
+        <v>76</v>
       </c>
       <c r="E2813" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="F2813" t="s">
         <v>11</v>
@@ -66824,10 +66824,10 @@
         <v>199</v>
       </c>
       <c r="D2814" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E2814" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F2814" t="s">
         <v>11</v>
@@ -66847,10 +66847,10 @@
         <v>199</v>
       </c>
       <c r="D2815" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="E2815" t="s">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="F2815" t="s">
         <v>11</v>
@@ -66870,10 +66870,10 @@
         <v>199</v>
       </c>
       <c r="D2816" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E2816" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F2816" t="s">
         <v>11</v>
@@ -66896,7 +66896,7 @@
         <v>171</v>
       </c>
       <c r="E2817" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="F2817" t="s">
         <v>11</v>
@@ -66916,13 +66916,13 @@
         <v>199</v>
       </c>
       <c r="D2818" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="E2818" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F2818" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2818" t="s">
         <v>12</v>
@@ -66939,13 +66939,13 @@
         <v>199</v>
       </c>
       <c r="D2819" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="E2819" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="F2819" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2819" t="s">
         <v>12</v>
@@ -66962,13 +66962,13 @@
         <v>199</v>
       </c>
       <c r="D2820" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E2820" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F2820" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2820" t="s">
         <v>12</v>
@@ -66985,13 +66985,13 @@
         <v>199</v>
       </c>
       <c r="D2821" t="s">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="E2821" t="s">
-        <v>22</v>
+        <v>105</v>
       </c>
       <c r="F2821" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2821" t="s">
         <v>12</v>
@@ -67008,10 +67008,10 @@
         <v>199</v>
       </c>
       <c r="D2822" t="s">
-        <v>144</v>
+        <v>21</v>
       </c>
       <c r="E2822" t="s">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="F2822" t="s">
         <v>11</v>
@@ -67031,10 +67031,10 @@
         <v>199</v>
       </c>
       <c r="D2823" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="E2823" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="F2823" t="s">
         <v>11</v>
@@ -67054,10 +67054,10 @@
         <v>199</v>
       </c>
       <c r="D2824" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="E2824" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="F2824" t="s">
         <v>11</v>
@@ -67077,10 +67077,10 @@
         <v>199</v>
       </c>
       <c r="D2825" t="s">
-        <v>76</v>
+        <v>164</v>
       </c>
       <c r="E2825" t="s">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="F2825" t="s">
         <v>11</v>
@@ -67100,13 +67100,13 @@
         <v>199</v>
       </c>
       <c r="D2826" t="s">
-        <v>168</v>
+        <v>76</v>
       </c>
       <c r="E2826" t="s">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="F2826" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2826" t="s">
         <v>12</v>
@@ -67123,10 +67123,10 @@
         <v>199</v>
       </c>
       <c r="D2827" t="s">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="E2827" t="s">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="F2827" t="s">
         <v>18</v>
@@ -67146,10 +67146,10 @@
         <v>199</v>
       </c>
       <c r="D2828" t="s">
-        <v>131</v>
+        <v>200</v>
       </c>
       <c r="E2828" t="s">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="F2828" t="s">
         <v>18</v>
@@ -67169,10 +67169,10 @@
         <v>199</v>
       </c>
       <c r="D2829" t="s">
-        <v>21</v>
+        <v>131</v>
       </c>
       <c r="E2829" t="s">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="F2829" t="s">
         <v>18</v>
@@ -67192,10 +67192,10 @@
         <v>199</v>
       </c>
       <c r="D2830" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E2830" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="F2830" t="s">
         <v>18</v>
@@ -67215,10 +67215,10 @@
         <v>199</v>
       </c>
       <c r="D2831" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="E2831" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="F2831" t="s">
         <v>18</v>
@@ -67238,10 +67238,10 @@
         <v>199</v>
       </c>
       <c r="D2832" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E2832" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2832" t="s">
         <v>18</v>
@@ -67252,22 +67252,22 @@
     </row>
     <row r="2833" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2833" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B2833" t="s">
-        <v>573</v>
+        <v>142</v>
       </c>
       <c r="C2833" t="s">
-        <v>75</v>
+        <v>199</v>
       </c>
       <c r="D2833" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="E2833" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="F2833" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2833" t="s">
         <v>12</v>
@@ -67284,13 +67284,13 @@
         <v>75</v>
       </c>
       <c r="D2834" t="s">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="E2834" t="s">
-        <v>257</v>
+        <v>79</v>
       </c>
       <c r="F2834" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2834" t="s">
         <v>12</v>
@@ -67310,13 +67310,13 @@
         <v>175</v>
       </c>
       <c r="E2835" t="s">
-        <v>176</v>
+        <v>257</v>
       </c>
       <c r="F2835" t="s">
         <v>18</v>
       </c>
       <c r="G2835" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2836" spans="1:7" x14ac:dyDescent="0.3">
@@ -67330,33 +67330,33 @@
         <v>75</v>
       </c>
       <c r="D2836" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E2836" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F2836" t="s">
         <v>18</v>
       </c>
       <c r="G2836" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2837" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2837" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B2837" t="s">
-        <v>285</v>
+        <v>573</v>
       </c>
       <c r="C2837" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
       <c r="D2837" t="s">
-        <v>24</v>
+        <v>164</v>
       </c>
       <c r="E2837" t="s">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="F2837" t="s">
         <v>18</v>
@@ -67376,13 +67376,13 @@
         <v>128</v>
       </c>
       <c r="D2838" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="E2838" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F2838" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2838" t="s">
         <v>12</v>
@@ -67399,10 +67399,10 @@
         <v>128</v>
       </c>
       <c r="D2839" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E2839" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2839" t="s">
         <v>11</v>
@@ -67422,10 +67422,10 @@
         <v>128</v>
       </c>
       <c r="D2840" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E2840" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2840" t="s">
         <v>11</v>
@@ -67445,10 +67445,10 @@
         <v>128</v>
       </c>
       <c r="D2841" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E2841" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F2841" t="s">
         <v>11</v>
@@ -67468,16 +67468,16 @@
         <v>128</v>
       </c>
       <c r="D2842" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="E2842" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F2842" t="s">
         <v>11</v>
       </c>
       <c r="G2842" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2843" spans="1:7" x14ac:dyDescent="0.3">
@@ -67491,16 +67491,16 @@
         <v>128</v>
       </c>
       <c r="D2843" t="s">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="E2843" t="s">
-        <v>14</v>
+        <v>64</v>
       </c>
       <c r="F2843" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2843" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2844" spans="1:7" x14ac:dyDescent="0.3">
@@ -67514,10 +67514,10 @@
         <v>128</v>
       </c>
       <c r="D2844" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="E2844" t="s">
-        <v>130</v>
+        <v>14</v>
       </c>
       <c r="F2844" t="s">
         <v>18</v>
@@ -67537,10 +67537,10 @@
         <v>128</v>
       </c>
       <c r="D2845" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E2845" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F2845" t="s">
         <v>18</v>
@@ -67560,16 +67560,16 @@
         <v>128</v>
       </c>
       <c r="D2846" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="E2846" t="s">
-        <v>64</v>
+        <v>134</v>
       </c>
       <c r="F2846" t="s">
         <v>18</v>
       </c>
       <c r="G2846" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2847" spans="1:7" x14ac:dyDescent="0.3">
@@ -67583,13 +67583,13 @@
         <v>128</v>
       </c>
       <c r="D2847" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="E2847" t="s">
-        <v>153</v>
+        <v>64</v>
       </c>
       <c r="F2847" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2847" t="s">
         <v>15</v>
@@ -67629,16 +67629,16 @@
         <v>128</v>
       </c>
       <c r="D2849" t="s">
-        <v>19</v>
+        <v>152</v>
       </c>
       <c r="E2849" t="s">
-        <v>20</v>
+        <v>153</v>
       </c>
       <c r="F2849" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2849" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2850" spans="1:7" x14ac:dyDescent="0.3">
@@ -67652,33 +67652,33 @@
         <v>128</v>
       </c>
       <c r="D2850" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="E2850" t="s">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="F2850" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2850" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2851" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2851" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B2851" t="s">
         <v>285</v>
       </c>
       <c r="C2851" t="s">
-        <v>234</v>
+        <v>128</v>
       </c>
       <c r="D2851" t="s">
-        <v>196</v>
+        <v>131</v>
       </c>
       <c r="E2851" t="s">
-        <v>197</v>
+        <v>132</v>
       </c>
       <c r="F2851" t="s">
         <v>11</v>
@@ -67698,16 +67698,16 @@
         <v>234</v>
       </c>
       <c r="D2852" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E2852" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="F2852" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2852" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2853" spans="1:7" x14ac:dyDescent="0.3">
@@ -67721,10 +67721,10 @@
         <v>234</v>
       </c>
       <c r="D2853" t="s">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="E2853" t="s">
-        <v>25</v>
+        <v>193</v>
       </c>
       <c r="F2853" t="s">
         <v>18</v>
@@ -67744,10 +67744,10 @@
         <v>234</v>
       </c>
       <c r="D2854" t="s">
-        <v>235</v>
+        <v>24</v>
       </c>
       <c r="E2854" t="s">
-        <v>236</v>
+        <v>25</v>
       </c>
       <c r="F2854" t="s">
         <v>18</v>
@@ -67767,10 +67767,10 @@
         <v>234</v>
       </c>
       <c r="D2855" t="s">
-        <v>13</v>
+        <v>235</v>
       </c>
       <c r="E2855" t="s">
-        <v>14</v>
+        <v>236</v>
       </c>
       <c r="F2855" t="s">
         <v>18</v>
@@ -67790,13 +67790,13 @@
         <v>234</v>
       </c>
       <c r="D2856" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="E2856" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="F2856" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2856" t="s">
         <v>12</v>
@@ -67813,10 +67813,10 @@
         <v>234</v>
       </c>
       <c r="D2857" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E2857" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F2857" t="s">
         <v>11</v>
@@ -67836,10 +67836,10 @@
         <v>234</v>
       </c>
       <c r="D2858" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E2858" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2858" t="s">
         <v>11</v>
@@ -67859,10 +67859,10 @@
         <v>234</v>
       </c>
       <c r="D2859" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E2859" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F2859" t="s">
         <v>11</v>
@@ -67882,10 +67882,10 @@
         <v>234</v>
       </c>
       <c r="D2860" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="E2860" t="s">
-        <v>237</v>
+        <v>20</v>
       </c>
       <c r="F2860" t="s">
         <v>11</v>
@@ -67905,13 +67905,13 @@
         <v>234</v>
       </c>
       <c r="D2861" t="s">
-        <v>19</v>
+        <v>196</v>
       </c>
       <c r="E2861" t="s">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="F2861" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2861" t="s">
         <v>12</v>
@@ -67919,22 +67919,22 @@
     </row>
     <row r="2862" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2862" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B2862" t="s">
-        <v>577</v>
+        <v>285</v>
       </c>
       <c r="C2862" t="s">
-        <v>149</v>
+        <v>234</v>
       </c>
       <c r="D2862" t="s">
-        <v>333</v>
+        <v>19</v>
       </c>
       <c r="E2862" t="s">
-        <v>334</v>
+        <v>20</v>
       </c>
       <c r="F2862" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2862" t="s">
         <v>12</v>
@@ -67951,16 +67951,16 @@
         <v>149</v>
       </c>
       <c r="D2863" t="s">
-        <v>182</v>
+        <v>333</v>
       </c>
       <c r="E2863" t="s">
-        <v>183</v>
+        <v>334</v>
       </c>
       <c r="F2863" t="s">
         <v>11</v>
       </c>
       <c r="G2863" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2864" spans="1:7" x14ac:dyDescent="0.3">
@@ -67974,16 +67974,16 @@
         <v>149</v>
       </c>
       <c r="D2864" t="s">
-        <v>446</v>
+        <v>182</v>
       </c>
       <c r="E2864" t="s">
-        <v>447</v>
+        <v>183</v>
       </c>
       <c r="F2864" t="s">
         <v>11</v>
       </c>
       <c r="G2864" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2865" spans="1:7" x14ac:dyDescent="0.3">
@@ -67997,16 +67997,16 @@
         <v>149</v>
       </c>
       <c r="D2865" t="s">
-        <v>106</v>
+        <v>446</v>
       </c>
       <c r="E2865" t="s">
-        <v>146</v>
+        <v>447</v>
       </c>
       <c r="F2865" t="s">
         <v>11</v>
       </c>
       <c r="G2865" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2866" spans="1:7" x14ac:dyDescent="0.3">
@@ -68020,10 +68020,10 @@
         <v>149</v>
       </c>
       <c r="D2866" t="s">
-        <v>144</v>
+        <v>106</v>
       </c>
       <c r="E2866" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F2866" t="s">
         <v>11</v>
@@ -68043,16 +68043,16 @@
         <v>149</v>
       </c>
       <c r="D2867" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="E2867" t="s">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="F2867" t="s">
         <v>11</v>
       </c>
       <c r="G2867" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2868" spans="1:7" x14ac:dyDescent="0.3">
@@ -68066,10 +68066,10 @@
         <v>149</v>
       </c>
       <c r="D2868" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="E2868" t="s">
-        <v>174</v>
+        <v>77</v>
       </c>
       <c r="F2868" t="s">
         <v>11</v>
@@ -68089,10 +68089,10 @@
         <v>149</v>
       </c>
       <c r="D2869" t="s">
-        <v>538</v>
+        <v>173</v>
       </c>
       <c r="E2869" t="s">
-        <v>541</v>
+        <v>174</v>
       </c>
       <c r="F2869" t="s">
         <v>11</v>
@@ -68112,10 +68112,10 @@
         <v>149</v>
       </c>
       <c r="D2870" t="s">
-        <v>175</v>
+        <v>538</v>
       </c>
       <c r="E2870" t="s">
-        <v>176</v>
+        <v>541</v>
       </c>
       <c r="F2870" t="s">
         <v>11</v>
@@ -68135,10 +68135,10 @@
         <v>149</v>
       </c>
       <c r="D2871" t="s">
-        <v>446</v>
+        <v>175</v>
       </c>
       <c r="E2871" t="s">
-        <v>447</v>
+        <v>176</v>
       </c>
       <c r="F2871" t="s">
         <v>11</v>
@@ -68158,13 +68158,13 @@
         <v>149</v>
       </c>
       <c r="D2872" t="s">
-        <v>21</v>
+        <v>446</v>
       </c>
       <c r="E2872" t="s">
-        <v>22</v>
+        <v>447</v>
       </c>
       <c r="F2872" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2872" t="s">
         <v>12</v>
@@ -68181,16 +68181,16 @@
         <v>149</v>
       </c>
       <c r="D2873" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="E2873" t="s">
-        <v>193</v>
+        <v>22</v>
       </c>
       <c r="F2873" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2873" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2874" spans="1:7" x14ac:dyDescent="0.3">
@@ -68204,10 +68204,10 @@
         <v>149</v>
       </c>
       <c r="D2874" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E2874" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F2874" t="s">
         <v>11</v>
@@ -68227,10 +68227,10 @@
         <v>149</v>
       </c>
       <c r="D2875" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="E2875" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F2875" t="s">
         <v>11</v>
@@ -68250,16 +68250,16 @@
         <v>149</v>
       </c>
       <c r="D2876" t="s">
-        <v>16</v>
+        <v>194</v>
       </c>
       <c r="E2876" t="s">
-        <v>17</v>
+        <v>195</v>
       </c>
       <c r="F2876" t="s">
         <v>11</v>
       </c>
       <c r="G2876" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2877" spans="1:7" x14ac:dyDescent="0.3">
@@ -68273,16 +68273,16 @@
         <v>149</v>
       </c>
       <c r="D2877" t="s">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="E2877" t="s">
-        <v>179</v>
+        <v>17</v>
       </c>
       <c r="F2877" t="s">
         <v>11</v>
       </c>
       <c r="G2877" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2878" spans="1:7" x14ac:dyDescent="0.3">
@@ -68296,16 +68296,16 @@
         <v>149</v>
       </c>
       <c r="D2878" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="E2878" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="F2878" t="s">
         <v>11</v>
       </c>
       <c r="G2878" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2879" spans="1:7" x14ac:dyDescent="0.3">
@@ -68319,10 +68319,10 @@
         <v>149</v>
       </c>
       <c r="D2879" t="s">
-        <v>100</v>
+        <v>129</v>
       </c>
       <c r="E2879" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="F2879" t="s">
         <v>11</v>
@@ -68342,10 +68342,10 @@
         <v>149</v>
       </c>
       <c r="D2880" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="E2880" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="F2880" t="s">
         <v>11</v>
@@ -68365,10 +68365,10 @@
         <v>149</v>
       </c>
       <c r="D2881" t="s">
-        <v>171</v>
+        <v>24</v>
       </c>
       <c r="E2881" t="s">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="F2881" t="s">
         <v>11</v>
@@ -68388,13 +68388,13 @@
         <v>149</v>
       </c>
       <c r="D2882" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="E2882" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="F2882" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2882" t="s">
         <v>12</v>
@@ -68411,13 +68411,13 @@
         <v>149</v>
       </c>
       <c r="D2883" t="s">
-        <v>335</v>
+        <v>110</v>
       </c>
       <c r="E2883" t="s">
-        <v>336</v>
+        <v>111</v>
       </c>
       <c r="F2883" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2883" t="s">
         <v>12</v>
@@ -68434,13 +68434,13 @@
         <v>149</v>
       </c>
       <c r="D2884" t="s">
-        <v>154</v>
+        <v>335</v>
       </c>
       <c r="E2884" t="s">
-        <v>170</v>
+        <v>336</v>
       </c>
       <c r="F2884" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2884" t="s">
         <v>12</v>
@@ -68457,13 +68457,13 @@
         <v>149</v>
       </c>
       <c r="D2885" t="s">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="E2885" t="s">
-        <v>10</v>
+        <v>170</v>
       </c>
       <c r="F2885" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2885" t="s">
         <v>12</v>
@@ -68480,10 +68480,10 @@
         <v>149</v>
       </c>
       <c r="D2886" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E2886" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2886" t="s">
         <v>11</v>
@@ -68509,7 +68509,7 @@
         <v>14</v>
       </c>
       <c r="F2887" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2887" t="s">
         <v>12</v>
@@ -68526,13 +68526,13 @@
         <v>149</v>
       </c>
       <c r="D2888" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E2888" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F2888" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2888" t="s">
         <v>12</v>
@@ -68555,7 +68555,7 @@
         <v>20</v>
       </c>
       <c r="F2889" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2889" t="s">
         <v>12</v>
@@ -68572,13 +68572,13 @@
         <v>149</v>
       </c>
       <c r="D2890" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="E2890" t="s">
-        <v>99</v>
+        <v>20</v>
       </c>
       <c r="F2890" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2890" t="s">
         <v>12</v>
@@ -68595,13 +68595,13 @@
         <v>149</v>
       </c>
       <c r="D2891" t="s">
-        <v>335</v>
+        <v>98</v>
       </c>
       <c r="E2891" t="s">
-        <v>336</v>
+        <v>99</v>
       </c>
       <c r="F2891" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2891" t="s">
         <v>12</v>
@@ -68618,10 +68618,10 @@
         <v>149</v>
       </c>
       <c r="D2892" t="s">
-        <v>24</v>
+        <v>335</v>
       </c>
       <c r="E2892" t="s">
-        <v>25</v>
+        <v>336</v>
       </c>
       <c r="F2892" t="s">
         <v>18</v>
@@ -68641,10 +68641,10 @@
         <v>149</v>
       </c>
       <c r="D2893" t="s">
-        <v>333</v>
+        <v>24</v>
       </c>
       <c r="E2893" t="s">
-        <v>334</v>
+        <v>25</v>
       </c>
       <c r="F2893" t="s">
         <v>18</v>
@@ -68655,25 +68655,25 @@
     </row>
     <row r="2894" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2894" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B2894" t="s">
         <v>577</v>
       </c>
       <c r="C2894" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="D2894" t="s">
-        <v>47</v>
+        <v>333</v>
       </c>
       <c r="E2894" t="s">
-        <v>48</v>
+        <v>334</v>
       </c>
       <c r="F2894" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2894" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2895" spans="1:7" x14ac:dyDescent="0.3">
@@ -68687,16 +68687,16 @@
         <v>199</v>
       </c>
       <c r="D2895" t="s">
-        <v>131</v>
+        <v>47</v>
       </c>
       <c r="E2895" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="F2895" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2895" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2896" spans="1:7" x14ac:dyDescent="0.3">
@@ -68710,10 +68710,10 @@
         <v>199</v>
       </c>
       <c r="D2896" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="E2896" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="F2896" t="s">
         <v>18</v>
@@ -68733,10 +68733,10 @@
         <v>199</v>
       </c>
       <c r="D2897" t="s">
-        <v>200</v>
+        <v>63</v>
       </c>
       <c r="E2897" t="s">
-        <v>201</v>
+        <v>64</v>
       </c>
       <c r="F2897" t="s">
         <v>18</v>
@@ -68756,16 +68756,16 @@
         <v>199</v>
       </c>
       <c r="D2898" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
       <c r="E2898" t="s">
-        <v>360</v>
+        <v>201</v>
       </c>
       <c r="F2898" t="s">
         <v>18</v>
       </c>
       <c r="G2898" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2899" spans="1:7" x14ac:dyDescent="0.3">
@@ -68779,10 +68779,10 @@
         <v>199</v>
       </c>
       <c r="D2899" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="E2899" t="s">
-        <v>214</v>
+        <v>360</v>
       </c>
       <c r="F2899" t="s">
         <v>18</v>
@@ -68802,10 +68802,10 @@
         <v>199</v>
       </c>
       <c r="D2900" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="E2900" t="s">
-        <v>248</v>
+        <v>214</v>
       </c>
       <c r="F2900" t="s">
         <v>18</v>
@@ -68825,10 +68825,10 @@
         <v>199</v>
       </c>
       <c r="D2901" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="E2901" t="s">
-        <v>212</v>
+        <v>248</v>
       </c>
       <c r="F2901" t="s">
         <v>18</v>
@@ -68848,16 +68848,16 @@
         <v>199</v>
       </c>
       <c r="D2902" t="s">
-        <v>342</v>
+        <v>211</v>
       </c>
       <c r="E2902" t="s">
-        <v>343</v>
+        <v>212</v>
       </c>
       <c r="F2902" t="s">
         <v>18</v>
       </c>
       <c r="G2902" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2903" spans="1:7" x14ac:dyDescent="0.3">
@@ -68871,16 +68871,16 @@
         <v>199</v>
       </c>
       <c r="D2903" t="s">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="E2903" t="s">
-        <v>77</v>
+        <v>343</v>
       </c>
       <c r="F2903" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2903" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2904" spans="1:7" x14ac:dyDescent="0.3">
@@ -68894,16 +68894,16 @@
         <v>199</v>
       </c>
       <c r="D2904" t="s">
-        <v>340</v>
+        <v>76</v>
       </c>
       <c r="E2904" t="s">
-        <v>341</v>
+        <v>77</v>
       </c>
       <c r="F2904" t="s">
         <v>11</v>
       </c>
       <c r="G2904" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2905" spans="1:7" x14ac:dyDescent="0.3">
@@ -68917,10 +68917,10 @@
         <v>199</v>
       </c>
       <c r="D2905" t="s">
-        <v>215</v>
+        <v>340</v>
       </c>
       <c r="E2905" t="s">
-        <v>246</v>
+        <v>341</v>
       </c>
       <c r="F2905" t="s">
         <v>11</v>
@@ -68940,10 +68940,10 @@
         <v>199</v>
       </c>
       <c r="D2906" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="E2906" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="F2906" t="s">
         <v>11</v>
@@ -68963,16 +68963,16 @@
         <v>199</v>
       </c>
       <c r="D2907" t="s">
-        <v>154</v>
+        <v>251</v>
       </c>
       <c r="E2907" t="s">
-        <v>170</v>
+        <v>252</v>
       </c>
       <c r="F2907" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2907" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2908" spans="1:7" x14ac:dyDescent="0.3">
@@ -68986,13 +68986,13 @@
         <v>199</v>
       </c>
       <c r="D2908" t="s">
-        <v>16</v>
+        <v>154</v>
       </c>
       <c r="E2908" t="s">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="F2908" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2908" t="s">
         <v>12</v>
@@ -69009,16 +69009,16 @@
         <v>199</v>
       </c>
       <c r="D2909" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="E2909" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="F2909" t="s">
         <v>11</v>
       </c>
       <c r="G2909" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2910" spans="1:7" x14ac:dyDescent="0.3">
@@ -69032,10 +69032,10 @@
         <v>199</v>
       </c>
       <c r="D2910" t="s">
-        <v>217</v>
+        <v>194</v>
       </c>
       <c r="E2910" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="F2910" t="s">
         <v>11</v>
@@ -69055,10 +69055,10 @@
         <v>199</v>
       </c>
       <c r="D2911" t="s">
-        <v>166</v>
+        <v>217</v>
       </c>
       <c r="E2911" t="s">
-        <v>179</v>
+        <v>218</v>
       </c>
       <c r="F2911" t="s">
         <v>11</v>
@@ -69078,10 +69078,10 @@
         <v>199</v>
       </c>
       <c r="D2912" t="s">
-        <v>217</v>
+        <v>166</v>
       </c>
       <c r="E2912" t="s">
-        <v>385</v>
+        <v>179</v>
       </c>
       <c r="F2912" t="s">
         <v>11</v>
@@ -69101,10 +69101,10 @@
         <v>199</v>
       </c>
       <c r="D2913" t="s">
-        <v>129</v>
+        <v>217</v>
       </c>
       <c r="E2913" t="s">
-        <v>130</v>
+        <v>385</v>
       </c>
       <c r="F2913" t="s">
         <v>11</v>
@@ -69124,10 +69124,10 @@
         <v>199</v>
       </c>
       <c r="D2914" t="s">
-        <v>340</v>
+        <v>129</v>
       </c>
       <c r="E2914" t="s">
-        <v>341</v>
+        <v>130</v>
       </c>
       <c r="F2914" t="s">
         <v>11</v>
@@ -69147,10 +69147,10 @@
         <v>199</v>
       </c>
       <c r="D2915" t="s">
-        <v>108</v>
+        <v>340</v>
       </c>
       <c r="E2915" t="s">
-        <v>240</v>
+        <v>341</v>
       </c>
       <c r="F2915" t="s">
         <v>11</v>
@@ -69170,16 +69170,16 @@
         <v>199</v>
       </c>
       <c r="D2916" t="s">
-        <v>538</v>
+        <v>108</v>
       </c>
       <c r="E2916" t="s">
-        <v>541</v>
+        <v>240</v>
       </c>
       <c r="F2916" t="s">
         <v>11</v>
       </c>
       <c r="G2916" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2917" spans="1:7" x14ac:dyDescent="0.3">
@@ -69193,10 +69193,10 @@
         <v>199</v>
       </c>
       <c r="D2917" t="s">
-        <v>446</v>
+        <v>538</v>
       </c>
       <c r="E2917" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F2917" t="s">
         <v>11</v>
@@ -69216,10 +69216,10 @@
         <v>199</v>
       </c>
       <c r="D2918" t="s">
-        <v>175</v>
+        <v>446</v>
       </c>
       <c r="E2918" t="s">
-        <v>176</v>
+        <v>540</v>
       </c>
       <c r="F2918" t="s">
         <v>11</v>
@@ -69239,10 +69239,10 @@
         <v>199</v>
       </c>
       <c r="D2919" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E2919" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F2919" t="s">
         <v>11</v>
@@ -69262,10 +69262,10 @@
         <v>199</v>
       </c>
       <c r="D2920" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="E2920" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="F2920" t="s">
         <v>11</v>
@@ -69285,10 +69285,10 @@
         <v>199</v>
       </c>
       <c r="D2921" t="s">
-        <v>171</v>
+        <v>110</v>
       </c>
       <c r="E2921" t="s">
-        <v>172</v>
+        <v>111</v>
       </c>
       <c r="F2921" t="s">
         <v>11</v>
@@ -69308,16 +69308,16 @@
         <v>199</v>
       </c>
       <c r="D2922" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="E2922" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="F2922" t="s">
         <v>11</v>
       </c>
       <c r="G2922" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2923" spans="1:7" x14ac:dyDescent="0.3">
@@ -69331,16 +69331,16 @@
         <v>199</v>
       </c>
       <c r="D2923" t="s">
-        <v>19</v>
+        <v>164</v>
       </c>
       <c r="E2923" t="s">
-        <v>20</v>
+        <v>165</v>
       </c>
       <c r="F2923" t="s">
         <v>11</v>
       </c>
       <c r="G2923" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2924" spans="1:7" x14ac:dyDescent="0.3">
@@ -69354,16 +69354,16 @@
         <v>199</v>
       </c>
       <c r="D2924" t="s">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="E2924" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="F2924" t="s">
         <v>11</v>
       </c>
       <c r="G2924" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2925" spans="1:7" x14ac:dyDescent="0.3">
@@ -69386,7 +69386,7 @@
         <v>11</v>
       </c>
       <c r="G2925" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2926" spans="1:7" x14ac:dyDescent="0.3">
@@ -69400,16 +69400,16 @@
         <v>199</v>
       </c>
       <c r="D2926" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="E2926" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="F2926" t="s">
         <v>11</v>
       </c>
       <c r="G2926" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2927" spans="1:7" x14ac:dyDescent="0.3">
@@ -69423,16 +69423,16 @@
         <v>199</v>
       </c>
       <c r="D2927" t="s">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="E2927" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="F2927" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2927" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2928" spans="1:7" x14ac:dyDescent="0.3">
@@ -69446,16 +69446,16 @@
         <v>199</v>
       </c>
       <c r="D2928" t="s">
-        <v>166</v>
+        <v>21</v>
       </c>
       <c r="E2928" t="s">
-        <v>179</v>
+        <v>22</v>
       </c>
       <c r="F2928" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2928" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2929" spans="1:7" x14ac:dyDescent="0.3">
@@ -69469,16 +69469,16 @@
         <v>199</v>
       </c>
       <c r="D2929" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="E2929" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="F2929" t="s">
         <v>11</v>
       </c>
       <c r="G2929" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2930" spans="1:7" x14ac:dyDescent="0.3">
@@ -69492,16 +69492,16 @@
         <v>199</v>
       </c>
       <c r="D2930" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="E2930" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="F2930" t="s">
         <v>11</v>
       </c>
       <c r="G2930" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2931" spans="1:7" x14ac:dyDescent="0.3">
@@ -69515,16 +69515,16 @@
         <v>199</v>
       </c>
       <c r="D2931" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="E2931" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="F2931" t="s">
         <v>11</v>
       </c>
       <c r="G2931" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2932" spans="1:7" x14ac:dyDescent="0.3">
@@ -69538,10 +69538,10 @@
         <v>199</v>
       </c>
       <c r="D2932" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E2932" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F2932" t="s">
         <v>11</v>
@@ -69561,10 +69561,10 @@
         <v>199</v>
       </c>
       <c r="D2933" t="s">
-        <v>333</v>
+        <v>9</v>
       </c>
       <c r="E2933" t="s">
-        <v>334</v>
+        <v>10</v>
       </c>
       <c r="F2933" t="s">
         <v>11</v>
@@ -69584,16 +69584,16 @@
         <v>199</v>
       </c>
       <c r="D2934" t="s">
-        <v>168</v>
+        <v>333</v>
       </c>
       <c r="E2934" t="s">
-        <v>245</v>
+        <v>334</v>
       </c>
       <c r="F2934" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2934" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2935" spans="1:7" x14ac:dyDescent="0.3">
@@ -69607,13 +69607,13 @@
         <v>199</v>
       </c>
       <c r="D2935" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E2935" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="F2935" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2935" t="s">
         <v>42</v>
@@ -69630,16 +69630,16 @@
         <v>199</v>
       </c>
       <c r="D2936" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="E2936" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="F2936" t="s">
         <v>11</v>
       </c>
       <c r="G2936" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2937" spans="1:7" x14ac:dyDescent="0.3">
@@ -69653,16 +69653,16 @@
         <v>199</v>
       </c>
       <c r="D2937" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="E2937" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="F2937" t="s">
         <v>11</v>
       </c>
       <c r="G2937" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2938" spans="1:7" x14ac:dyDescent="0.3">
@@ -69676,16 +69676,16 @@
         <v>199</v>
       </c>
       <c r="D2938" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="E2938" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="F2938" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2938" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2939" spans="1:7" x14ac:dyDescent="0.3">
@@ -69699,10 +69699,10 @@
         <v>199</v>
       </c>
       <c r="D2939" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E2939" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="F2939" t="s">
         <v>18</v>
@@ -69722,10 +69722,10 @@
         <v>199</v>
       </c>
       <c r="D2940" t="s">
-        <v>19</v>
+        <v>110</v>
       </c>
       <c r="E2940" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="F2940" t="s">
         <v>18</v>
@@ -69745,13 +69745,13 @@
         <v>199</v>
       </c>
       <c r="D2941" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E2941" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F2941" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2941" t="s">
         <v>12</v>
@@ -69774,7 +69774,7 @@
         <v>14</v>
       </c>
       <c r="F2942" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2942" t="s">
         <v>12</v>
@@ -69791,16 +69791,16 @@
         <v>199</v>
       </c>
       <c r="D2943" t="s">
-        <v>106</v>
+        <v>13</v>
       </c>
       <c r="E2943" t="s">
-        <v>107</v>
+        <v>14</v>
       </c>
       <c r="F2943" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2943" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2944" spans="1:7" x14ac:dyDescent="0.3">
@@ -69814,16 +69814,16 @@
         <v>199</v>
       </c>
       <c r="D2944" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="E2944" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="F2944" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2944" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2945" spans="1:7" x14ac:dyDescent="0.3">
@@ -69837,10 +69837,10 @@
         <v>199</v>
       </c>
       <c r="D2945" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E2945" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="F2945" t="s">
         <v>18</v>
@@ -69860,10 +69860,10 @@
         <v>199</v>
       </c>
       <c r="D2946" t="s">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="E2946" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="F2946" t="s">
         <v>18</v>
@@ -69883,13 +69883,13 @@
         <v>199</v>
       </c>
       <c r="D2947" t="s">
-        <v>247</v>
+        <v>16</v>
       </c>
       <c r="E2947" t="s">
-        <v>248</v>
+        <v>17</v>
       </c>
       <c r="F2947" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2947" t="s">
         <v>12</v>
@@ -69906,16 +69906,16 @@
         <v>199</v>
       </c>
       <c r="D2948" t="s">
-        <v>144</v>
+        <v>247</v>
       </c>
       <c r="E2948" t="s">
-        <v>145</v>
+        <v>248</v>
       </c>
       <c r="F2948" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2948" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2949" spans="1:7" x14ac:dyDescent="0.3">
@@ -69929,16 +69929,16 @@
         <v>199</v>
       </c>
       <c r="D2949" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="E2949" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="F2949" t="s">
         <v>18</v>
       </c>
       <c r="G2949" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2950" spans="1:7" x14ac:dyDescent="0.3">
@@ -69952,16 +69952,16 @@
         <v>199</v>
       </c>
       <c r="D2950" t="s">
-        <v>213</v>
+        <v>106</v>
       </c>
       <c r="E2950" t="s">
-        <v>214</v>
+        <v>107</v>
       </c>
       <c r="F2950" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2950" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2951" spans="1:7" x14ac:dyDescent="0.3">
@@ -69975,10 +69975,10 @@
         <v>199</v>
       </c>
       <c r="D2951" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="E2951" t="s">
-        <v>22</v>
+        <v>214</v>
       </c>
       <c r="F2951" t="s">
         <v>11</v>
@@ -69989,25 +69989,25 @@
     </row>
     <row r="2952" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2952" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B2952" t="s">
         <v>577</v>
       </c>
       <c r="C2952" t="s">
-        <v>327</v>
+        <v>199</v>
       </c>
       <c r="D2952" t="s">
-        <v>182</v>
+        <v>21</v>
       </c>
       <c r="E2952" t="s">
-        <v>183</v>
+        <v>22</v>
       </c>
       <c r="F2952" t="s">
         <v>11</v>
       </c>
       <c r="G2952" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2953" spans="1:7" x14ac:dyDescent="0.3">
@@ -70021,13 +70021,13 @@
         <v>327</v>
       </c>
       <c r="D2953" t="s">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="E2953" t="s">
-        <v>157</v>
+        <v>183</v>
       </c>
       <c r="F2953" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2953" t="s">
         <v>15</v>
@@ -70044,10 +70044,10 @@
         <v>327</v>
       </c>
       <c r="D2954" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="E2954" t="s">
-        <v>197</v>
+        <v>157</v>
       </c>
       <c r="F2954" t="s">
         <v>18</v>
@@ -70067,10 +70067,10 @@
         <v>327</v>
       </c>
       <c r="D2955" t="s">
-        <v>152</v>
+        <v>196</v>
       </c>
       <c r="E2955" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="F2955" t="s">
         <v>18</v>
@@ -70090,13 +70090,13 @@
         <v>327</v>
       </c>
       <c r="D2956" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="E2956" t="s">
-        <v>99</v>
+        <v>153</v>
       </c>
       <c r="F2956" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2956" t="s">
         <v>15</v>
@@ -70113,16 +70113,16 @@
         <v>327</v>
       </c>
       <c r="D2957" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="E2957" t="s">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="F2957" t="s">
         <v>11</v>
       </c>
       <c r="G2957" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2958" spans="1:7" x14ac:dyDescent="0.3">
@@ -70136,10 +70136,10 @@
         <v>327</v>
       </c>
       <c r="D2958" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E2958" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F2958" t="s">
         <v>11</v>
@@ -70159,10 +70159,10 @@
         <v>327</v>
       </c>
       <c r="D2959" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E2959" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F2959" t="s">
         <v>11</v>
@@ -70182,10 +70182,10 @@
         <v>327</v>
       </c>
       <c r="D2960" t="s">
-        <v>129</v>
+        <v>19</v>
       </c>
       <c r="E2960" t="s">
-        <v>130</v>
+        <v>20</v>
       </c>
       <c r="F2960" t="s">
         <v>11</v>
@@ -70205,16 +70205,16 @@
         <v>327</v>
       </c>
       <c r="D2961" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="E2961" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="F2961" t="s">
         <v>11</v>
       </c>
       <c r="G2961" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2962" spans="1:7" x14ac:dyDescent="0.3">
@@ -70228,13 +70228,13 @@
         <v>327</v>
       </c>
       <c r="D2962" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="E2962" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="F2962" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2962" t="s">
         <v>15</v>
@@ -70251,16 +70251,16 @@
         <v>327</v>
       </c>
       <c r="D2963" t="s">
-        <v>13</v>
+        <v>158</v>
       </c>
       <c r="E2963" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="F2963" t="s">
         <v>18</v>
       </c>
       <c r="G2963" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2964" spans="1:7" x14ac:dyDescent="0.3">
@@ -70274,13 +70274,13 @@
         <v>327</v>
       </c>
       <c r="D2964" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E2964" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F2964" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2964" t="s">
         <v>12</v>
@@ -70297,16 +70297,16 @@
         <v>327</v>
       </c>
       <c r="D2965" t="s">
-        <v>194</v>
+        <v>16</v>
       </c>
       <c r="E2965" t="s">
-        <v>195</v>
+        <v>17</v>
       </c>
       <c r="F2965" t="s">
         <v>11</v>
       </c>
       <c r="G2965" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2966" spans="1:7" x14ac:dyDescent="0.3">
@@ -70320,10 +70320,10 @@
         <v>327</v>
       </c>
       <c r="D2966" t="s">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="E2966" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="F2966" t="s">
         <v>11</v>
@@ -70343,10 +70343,10 @@
         <v>327</v>
       </c>
       <c r="D2967" t="s">
-        <v>106</v>
+        <v>166</v>
       </c>
       <c r="E2967" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="F2967" t="s">
         <v>11</v>
@@ -70366,16 +70366,16 @@
         <v>327</v>
       </c>
       <c r="D2968" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="E2968" t="s">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="F2968" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2968" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2969" spans="1:7" x14ac:dyDescent="0.3">
@@ -70389,16 +70389,16 @@
         <v>327</v>
       </c>
       <c r="D2969" t="s">
-        <v>190</v>
+        <v>24</v>
       </c>
       <c r="E2969" t="s">
-        <v>191</v>
+        <v>25</v>
       </c>
       <c r="F2969" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2969" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2970" spans="1:7" x14ac:dyDescent="0.3">
@@ -70412,16 +70412,16 @@
         <v>327</v>
       </c>
       <c r="D2970" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="E2970" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="F2970" t="s">
         <v>11</v>
       </c>
       <c r="G2970" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2971" spans="1:7" x14ac:dyDescent="0.3">
@@ -70435,16 +70435,16 @@
         <v>327</v>
       </c>
       <c r="D2971" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="E2971" t="s">
-        <v>99</v>
+        <v>170</v>
       </c>
       <c r="F2971" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2971" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2972" spans="1:7" x14ac:dyDescent="0.3">
@@ -70458,10 +70458,10 @@
         <v>327</v>
       </c>
       <c r="D2972" t="s">
-        <v>180</v>
+        <v>98</v>
       </c>
       <c r="E2972" t="s">
-        <v>181</v>
+        <v>99</v>
       </c>
       <c r="F2972" t="s">
         <v>18</v>
@@ -70481,16 +70481,16 @@
         <v>327</v>
       </c>
       <c r="D2973" t="s">
-        <v>19</v>
+        <v>180</v>
       </c>
       <c r="E2973" t="s">
-        <v>20</v>
+        <v>181</v>
       </c>
       <c r="F2973" t="s">
         <v>18</v>
       </c>
       <c r="G2973" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2974" spans="1:7" x14ac:dyDescent="0.3">
@@ -70504,16 +70504,16 @@
         <v>327</v>
       </c>
       <c r="D2974" t="s">
-        <v>144</v>
+        <v>19</v>
       </c>
       <c r="E2974" t="s">
-        <v>145</v>
+        <v>20</v>
       </c>
       <c r="F2974" t="s">
         <v>18</v>
       </c>
       <c r="G2974" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2975" spans="1:7" x14ac:dyDescent="0.3">
@@ -70527,16 +70527,16 @@
         <v>327</v>
       </c>
       <c r="D2975" t="s">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="E2975" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="F2975" t="s">
         <v>18</v>
       </c>
       <c r="G2975" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2976" spans="1:7" x14ac:dyDescent="0.3">
@@ -70550,16 +70550,16 @@
         <v>327</v>
       </c>
       <c r="D2976" t="s">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="E2976" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="F2976" t="s">
         <v>18</v>
       </c>
       <c r="G2976" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2977" spans="1:7" x14ac:dyDescent="0.3">
@@ -70573,10 +70573,10 @@
         <v>327</v>
       </c>
       <c r="D2977" t="s">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="E2977" t="s">
-        <v>161</v>
+        <v>101</v>
       </c>
       <c r="F2977" t="s">
         <v>18</v>
@@ -70596,10 +70596,10 @@
         <v>327</v>
       </c>
       <c r="D2978" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="E2978" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="F2978" t="s">
         <v>18</v>
@@ -70619,16 +70619,16 @@
         <v>327</v>
       </c>
       <c r="D2979" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="E2979" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="F2979" t="s">
         <v>18</v>
       </c>
       <c r="G2979" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2980" spans="1:7" x14ac:dyDescent="0.3">
@@ -70642,10 +70642,10 @@
         <v>327</v>
       </c>
       <c r="D2980" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E2980" t="s">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="F2980" t="s">
         <v>18</v>
@@ -70665,16 +70665,16 @@
         <v>327</v>
       </c>
       <c r="D2981" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E2981" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="F2981" t="s">
         <v>18</v>
       </c>
       <c r="G2981" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2982" spans="1:7" x14ac:dyDescent="0.3">
@@ -70688,10 +70688,10 @@
         <v>327</v>
       </c>
       <c r="D2982" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="E2982" t="s">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="F2982" t="s">
         <v>18</v>
@@ -70711,10 +70711,10 @@
         <v>327</v>
       </c>
       <c r="D2983" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E2983" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="F2983" t="s">
         <v>18</v>
@@ -70734,10 +70734,10 @@
         <v>327</v>
       </c>
       <c r="D2984" t="s">
-        <v>166</v>
+        <v>123</v>
       </c>
       <c r="E2984" t="s">
-        <v>179</v>
+        <v>124</v>
       </c>
       <c r="F2984" t="s">
         <v>18</v>
@@ -70757,16 +70757,16 @@
         <v>327</v>
       </c>
       <c r="D2985" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="E2985" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="F2985" t="s">
         <v>18</v>
       </c>
       <c r="G2985" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2986" spans="1:7" x14ac:dyDescent="0.3">
@@ -70780,13 +70780,13 @@
         <v>327</v>
       </c>
       <c r="D2986" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="E2986" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="F2986" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2986" t="s">
         <v>12</v>
@@ -70803,16 +70803,16 @@
         <v>327</v>
       </c>
       <c r="D2987" t="s">
-        <v>92</v>
+        <v>184</v>
       </c>
       <c r="E2987" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="F2987" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G2987" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2988" spans="1:7" x14ac:dyDescent="0.3">
@@ -70826,13 +70826,13 @@
         <v>327</v>
       </c>
       <c r="D2988" t="s">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="E2988" t="s">
-        <v>193</v>
+        <v>93</v>
       </c>
       <c r="F2988" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G2988" t="s">
         <v>15</v>
@@ -70849,10 +70849,10 @@
         <v>327</v>
       </c>
       <c r="D2989" t="s">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="E2989" t="s">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="F2989" t="s">
         <v>11</v>
@@ -70872,10 +70872,10 @@
         <v>327</v>
       </c>
       <c r="D2990" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E2990" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F2990" t="s">
         <v>11</v>
@@ -70895,10 +70895,10 @@
         <v>327</v>
       </c>
       <c r="D2991" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="E2991" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="F2991" t="s">
         <v>11</v>
@@ -70918,10 +70918,10 @@
         <v>327</v>
       </c>
       <c r="D2992" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E2992" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F2992" t="s">
         <v>11</v>
@@ -70941,10 +70941,10 @@
         <v>327</v>
       </c>
       <c r="D2993" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E2993" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="F2993" t="s">
         <v>11</v>
@@ -70964,10 +70964,10 @@
         <v>327</v>
       </c>
       <c r="D2994" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E2994" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F2994" t="s">
         <v>11</v>
@@ -70987,10 +70987,10 @@
         <v>327</v>
       </c>
       <c r="D2995" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="E2995" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="F2995" t="s">
         <v>11</v>
@@ -71010,10 +71010,10 @@
         <v>327</v>
       </c>
       <c r="D2996" t="s">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="E2996" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="F2996" t="s">
         <v>11</v>
@@ -71033,10 +71033,10 @@
         <v>327</v>
       </c>
       <c r="D2997" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E2997" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F2997" t="s">
         <v>11</v>
@@ -71056,16 +71056,16 @@
         <v>327</v>
       </c>
       <c r="D2998" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E2998" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F2998" t="s">
         <v>11</v>
       </c>
       <c r="G2998" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2999" spans="1:7" x14ac:dyDescent="0.3">
@@ -71079,16 +71079,16 @@
         <v>327</v>
       </c>
       <c r="D2999" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="E2999" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="F2999" t="s">
         <v>11</v>
       </c>
       <c r="G2999" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3000" spans="1:7" x14ac:dyDescent="0.3">
@@ -71102,10 +71102,10 @@
         <v>327</v>
       </c>
       <c r="D3000" t="s">
-        <v>177</v>
+        <v>150</v>
       </c>
       <c r="E3000" t="s">
-        <v>178</v>
+        <v>151</v>
       </c>
       <c r="F3000" t="s">
         <v>11</v>
@@ -71125,10 +71125,10 @@
         <v>327</v>
       </c>
       <c r="D3001" t="s">
-        <v>24</v>
+        <v>177</v>
       </c>
       <c r="E3001" t="s">
-        <v>25</v>
+        <v>178</v>
       </c>
       <c r="F3001" t="s">
         <v>11</v>
@@ -71148,16 +71148,16 @@
         <v>327</v>
       </c>
       <c r="D3002" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="E3002" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="F3002" t="s">
         <v>11</v>
       </c>
       <c r="G3002" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3003" spans="1:7" x14ac:dyDescent="0.3">
@@ -71171,10 +71171,10 @@
         <v>327</v>
       </c>
       <c r="D3003" t="s">
-        <v>166</v>
+        <v>76</v>
       </c>
       <c r="E3003" t="s">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="F3003" t="s">
         <v>11</v>
@@ -71185,22 +71185,22 @@
     </row>
     <row r="3004" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3004" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B3004" t="s">
-        <v>285</v>
+        <v>577</v>
       </c>
       <c r="C3004" t="s">
-        <v>149</v>
+        <v>327</v>
       </c>
       <c r="D3004" t="s">
-        <v>13</v>
+        <v>166</v>
       </c>
       <c r="E3004" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="F3004" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3004" t="s">
         <v>12</v>
@@ -71217,10 +71217,10 @@
         <v>149</v>
       </c>
       <c r="D3005" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E3005" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F3005" t="s">
         <v>18</v>
@@ -71240,10 +71240,10 @@
         <v>149</v>
       </c>
       <c r="D3006" t="s">
-        <v>110</v>
+        <v>21</v>
       </c>
       <c r="E3006" t="s">
-        <v>111</v>
+        <v>22</v>
       </c>
       <c r="F3006" t="s">
         <v>18</v>
@@ -71263,10 +71263,10 @@
         <v>149</v>
       </c>
       <c r="D3007" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="E3007" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="F3007" t="s">
         <v>18</v>
@@ -71286,10 +71286,10 @@
         <v>149</v>
       </c>
       <c r="D3008" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E3008" t="s">
-        <v>25</v>
+        <v>151</v>
       </c>
       <c r="F3008" t="s">
         <v>18</v>
@@ -71309,10 +71309,10 @@
         <v>149</v>
       </c>
       <c r="D3009" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="E3009" t="s">
-        <v>179</v>
+        <v>25</v>
       </c>
       <c r="F3009" t="s">
         <v>18</v>
@@ -71332,10 +71332,10 @@
         <v>149</v>
       </c>
       <c r="D3010" t="s">
-        <v>19</v>
+        <v>166</v>
       </c>
       <c r="E3010" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
       <c r="F3010" t="s">
         <v>18</v>
@@ -71355,10 +71355,10 @@
         <v>149</v>
       </c>
       <c r="D3011" t="s">
-        <v>180</v>
+        <v>19</v>
       </c>
       <c r="E3011" t="s">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="F3011" t="s">
         <v>18</v>
@@ -71378,10 +71378,10 @@
         <v>149</v>
       </c>
       <c r="D3012" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="E3012" t="s">
-        <v>99</v>
+        <v>181</v>
       </c>
       <c r="F3012" t="s">
         <v>18</v>
@@ -71401,10 +71401,10 @@
         <v>149</v>
       </c>
       <c r="D3013" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="E3013" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="F3013" t="s">
         <v>18</v>
@@ -71424,13 +71424,13 @@
         <v>149</v>
       </c>
       <c r="D3014" t="s">
-        <v>98</v>
+        <v>154</v>
       </c>
       <c r="E3014" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="F3014" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3014" t="s">
         <v>12</v>
@@ -71447,13 +71447,13 @@
         <v>149</v>
       </c>
       <c r="D3015" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3015" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3015" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3015" t="s">
         <v>12</v>
@@ -71470,10 +71470,10 @@
         <v>149</v>
       </c>
       <c r="D3016" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="E3016" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="F3016" t="s">
         <v>18</v>
@@ -71493,10 +71493,10 @@
         <v>149</v>
       </c>
       <c r="D3017" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="E3017" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="F3017" t="s">
         <v>18</v>
@@ -71516,13 +71516,13 @@
         <v>149</v>
       </c>
       <c r="D3018" t="s">
-        <v>182</v>
+        <v>156</v>
       </c>
       <c r="E3018" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="F3018" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3018" t="s">
         <v>12</v>
@@ -71539,10 +71539,10 @@
         <v>149</v>
       </c>
       <c r="D3019" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="E3019" t="s">
-        <v>145</v>
+        <v>183</v>
       </c>
       <c r="F3019" t="s">
         <v>11</v>
@@ -71562,10 +71562,10 @@
         <v>149</v>
       </c>
       <c r="D3020" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="E3020" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="F3020" t="s">
         <v>11</v>
@@ -71585,10 +71585,10 @@
         <v>149</v>
       </c>
       <c r="D3021" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="E3021" t="s">
-        <v>20</v>
+        <v>107</v>
       </c>
       <c r="F3021" t="s">
         <v>11</v>
@@ -71608,10 +71608,10 @@
         <v>149</v>
       </c>
       <c r="D3022" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E3022" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F3022" t="s">
         <v>11</v>
@@ -71631,13 +71631,13 @@
         <v>149</v>
       </c>
       <c r="D3023" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="E3023" t="s">
-        <v>159</v>
+        <v>14</v>
       </c>
       <c r="F3023" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3023" t="s">
         <v>12</v>
@@ -71654,13 +71654,13 @@
         <v>149</v>
       </c>
       <c r="D3024" t="s">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="E3024" t="s">
-        <v>178</v>
+        <v>159</v>
       </c>
       <c r="F3024" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3024" t="s">
         <v>12</v>
@@ -71677,13 +71677,13 @@
         <v>149</v>
       </c>
       <c r="D3025" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="E3025" t="s">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="F3025" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3025" t="s">
         <v>12</v>
@@ -71700,13 +71700,13 @@
         <v>149</v>
       </c>
       <c r="D3026" t="s">
-        <v>16</v>
+        <v>131</v>
       </c>
       <c r="E3026" t="s">
-        <v>17</v>
+        <v>132</v>
       </c>
       <c r="F3026" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3026" t="s">
         <v>12</v>
@@ -71723,13 +71723,13 @@
         <v>149</v>
       </c>
       <c r="D3027" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
       <c r="E3027" t="s">
-        <v>161</v>
+        <v>17</v>
       </c>
       <c r="F3027" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3027" t="s">
         <v>12</v>
@@ -71746,10 +71746,10 @@
         <v>149</v>
       </c>
       <c r="D3028" t="s">
-        <v>58</v>
+        <v>160</v>
       </c>
       <c r="E3028" t="s">
-        <v>59</v>
+        <v>161</v>
       </c>
       <c r="F3028" t="s">
         <v>18</v>
@@ -71769,10 +71769,10 @@
         <v>149</v>
       </c>
       <c r="D3029" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="E3029" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="F3029" t="s">
         <v>18</v>
@@ -71792,10 +71792,10 @@
         <v>149</v>
       </c>
       <c r="D3030" t="s">
-        <v>196</v>
+        <v>152</v>
       </c>
       <c r="E3030" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="F3030" t="s">
         <v>18</v>
@@ -71815,10 +71815,10 @@
         <v>149</v>
       </c>
       <c r="D3031" t="s">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="E3031" t="s">
-        <v>124</v>
+        <v>197</v>
       </c>
       <c r="F3031" t="s">
         <v>18</v>
@@ -71838,13 +71838,13 @@
         <v>149</v>
       </c>
       <c r="D3032" t="s">
-        <v>9</v>
+        <v>123</v>
       </c>
       <c r="E3032" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
       <c r="F3032" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3032" t="s">
         <v>12</v>
@@ -71861,10 +71861,10 @@
         <v>149</v>
       </c>
       <c r="D3033" t="s">
-        <v>166</v>
+        <v>9</v>
       </c>
       <c r="E3033" t="s">
-        <v>167</v>
+        <v>10</v>
       </c>
       <c r="F3033" t="s">
         <v>11</v>
@@ -71884,10 +71884,10 @@
         <v>149</v>
       </c>
       <c r="D3034" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="E3034" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="F3034" t="s">
         <v>11</v>
@@ -71907,10 +71907,10 @@
         <v>149</v>
       </c>
       <c r="D3035" t="s">
-        <v>175</v>
+        <v>194</v>
       </c>
       <c r="E3035" t="s">
-        <v>176</v>
+        <v>195</v>
       </c>
       <c r="F3035" t="s">
         <v>11</v>
@@ -71930,10 +71930,10 @@
         <v>149</v>
       </c>
       <c r="D3036" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="E3036" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="F3036" t="s">
         <v>11</v>
@@ -71953,10 +71953,10 @@
         <v>149</v>
       </c>
       <c r="D3037" t="s">
-        <v>37</v>
+        <v>192</v>
       </c>
       <c r="E3037" t="s">
-        <v>294</v>
+        <v>193</v>
       </c>
       <c r="F3037" t="s">
         <v>11</v>
@@ -71976,10 +71976,10 @@
         <v>149</v>
       </c>
       <c r="D3038" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3038" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F3038" t="s">
         <v>11</v>
@@ -71999,10 +71999,10 @@
         <v>149</v>
       </c>
       <c r="D3039" t="s">
-        <v>186</v>
+        <v>35</v>
       </c>
       <c r="E3039" t="s">
-        <v>187</v>
+        <v>295</v>
       </c>
       <c r="F3039" t="s">
         <v>11</v>
@@ -72022,10 +72022,10 @@
         <v>149</v>
       </c>
       <c r="D3040" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="E3040" t="s">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="F3040" t="s">
         <v>11</v>
@@ -72045,10 +72045,10 @@
         <v>149</v>
       </c>
       <c r="D3041" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="E3041" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
       <c r="F3041" t="s">
         <v>11</v>
@@ -72068,13 +72068,13 @@
         <v>149</v>
       </c>
       <c r="D3042" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="E3042" t="s">
-        <v>50</v>
+        <v>189</v>
       </c>
       <c r="F3042" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3042" t="s">
         <v>12</v>
@@ -72091,10 +72091,10 @@
         <v>149</v>
       </c>
       <c r="D3043" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3043" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F3043" t="s">
         <v>18</v>
@@ -72114,10 +72114,10 @@
         <v>149</v>
       </c>
       <c r="D3044" t="s">
-        <v>162</v>
+        <v>51</v>
       </c>
       <c r="E3044" t="s">
-        <v>163</v>
+        <v>52</v>
       </c>
       <c r="F3044" t="s">
         <v>18</v>
@@ -72137,13 +72137,13 @@
         <v>149</v>
       </c>
       <c r="D3045" t="s">
-        <v>33</v>
+        <v>162</v>
       </c>
       <c r="E3045" t="s">
-        <v>34</v>
+        <v>163</v>
       </c>
       <c r="F3045" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3045" t="s">
         <v>12</v>
@@ -72160,13 +72160,13 @@
         <v>149</v>
       </c>
       <c r="D3046" t="s">
-        <v>168</v>
+        <v>33</v>
       </c>
       <c r="E3046" t="s">
-        <v>169</v>
+        <v>34</v>
       </c>
       <c r="F3046" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3046" t="s">
         <v>12</v>
@@ -72183,16 +72183,16 @@
         <v>149</v>
       </c>
       <c r="D3047" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E3047" t="s">
-        <v>305</v>
+        <v>169</v>
       </c>
       <c r="F3047" t="s">
         <v>18</v>
       </c>
       <c r="G3047" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3048" spans="1:7" x14ac:dyDescent="0.3">
@@ -72206,16 +72206,16 @@
         <v>149</v>
       </c>
       <c r="D3048" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E3048" t="s">
-        <v>170</v>
+        <v>305</v>
       </c>
       <c r="F3048" t="s">
         <v>18</v>
       </c>
       <c r="G3048" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3049" spans="1:7" x14ac:dyDescent="0.3">
@@ -72229,13 +72229,13 @@
         <v>149</v>
       </c>
       <c r="D3049" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E3049" t="s">
-        <v>151</v>
+        <v>170</v>
       </c>
       <c r="F3049" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3049" t="s">
         <v>12</v>
@@ -72252,10 +72252,10 @@
         <v>149</v>
       </c>
       <c r="D3050" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="E3050" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="F3050" t="s">
         <v>11</v>
@@ -72275,10 +72275,10 @@
         <v>149</v>
       </c>
       <c r="D3051" t="s">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="E3051" t="s">
-        <v>130</v>
+        <v>179</v>
       </c>
       <c r="F3051" t="s">
         <v>11</v>
@@ -72298,10 +72298,10 @@
         <v>149</v>
       </c>
       <c r="D3052" t="s">
-        <v>190</v>
+        <v>129</v>
       </c>
       <c r="E3052" t="s">
-        <v>191</v>
+        <v>130</v>
       </c>
       <c r="F3052" t="s">
         <v>11</v>
@@ -72321,10 +72321,10 @@
         <v>149</v>
       </c>
       <c r="D3053" t="s">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="E3053" t="s">
-        <v>293</v>
+        <v>191</v>
       </c>
       <c r="F3053" t="s">
         <v>11</v>
@@ -72344,10 +72344,10 @@
         <v>149</v>
       </c>
       <c r="D3054" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E3054" t="s">
-        <v>25</v>
+        <v>293</v>
       </c>
       <c r="F3054" t="s">
         <v>11</v>
@@ -72367,10 +72367,10 @@
         <v>149</v>
       </c>
       <c r="D3055" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E3055" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="F3055" t="s">
         <v>11</v>
@@ -72390,10 +72390,10 @@
         <v>149</v>
       </c>
       <c r="D3056" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E3056" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F3056" t="s">
         <v>11</v>
@@ -72413,10 +72413,10 @@
         <v>149</v>
       </c>
       <c r="D3057" t="s">
-        <v>184</v>
+        <v>104</v>
       </c>
       <c r="E3057" t="s">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="F3057" t="s">
         <v>11</v>
@@ -72436,10 +72436,10 @@
         <v>149</v>
       </c>
       <c r="D3058" t="s">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="E3058" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="F3058" t="s">
         <v>11</v>
@@ -72459,10 +72459,10 @@
         <v>149</v>
       </c>
       <c r="D3059" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="E3059" t="s">
-        <v>170</v>
+        <v>111</v>
       </c>
       <c r="F3059" t="s">
         <v>11</v>
@@ -72485,7 +72485,7 @@
         <v>154</v>
       </c>
       <c r="E3060" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="F3060" t="s">
         <v>11</v>
@@ -72505,10 +72505,10 @@
         <v>149</v>
       </c>
       <c r="D3061" t="s">
-        <v>76</v>
+        <v>154</v>
       </c>
       <c r="E3061" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="F3061" t="s">
         <v>11</v>
@@ -72528,10 +72528,10 @@
         <v>149</v>
       </c>
       <c r="D3062" t="s">
-        <v>173</v>
+        <v>76</v>
       </c>
       <c r="E3062" t="s">
-        <v>174</v>
+        <v>77</v>
       </c>
       <c r="F3062" t="s">
         <v>11</v>
@@ -72551,10 +72551,10 @@
         <v>149</v>
       </c>
       <c r="D3063" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E3063" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F3063" t="s">
         <v>11</v>
@@ -72565,22 +72565,22 @@
     </row>
     <row r="3064" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3064" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B3064" t="s">
         <v>285</v>
       </c>
       <c r="C3064" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="D3064" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
       <c r="E3064" t="s">
-        <v>17</v>
+        <v>172</v>
       </c>
       <c r="F3064" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3064" t="s">
         <v>12</v>
@@ -72597,10 +72597,10 @@
         <v>199</v>
       </c>
       <c r="D3065" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="E3065" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F3065" t="s">
         <v>18</v>
@@ -72620,16 +72620,16 @@
         <v>199</v>
       </c>
       <c r="D3066" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="E3066" t="s">
-        <v>101</v>
+        <v>25</v>
       </c>
       <c r="F3066" t="s">
         <v>18</v>
       </c>
       <c r="G3066" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3067" spans="1:7" x14ac:dyDescent="0.3">
@@ -72643,16 +72643,16 @@
         <v>199</v>
       </c>
       <c r="D3067" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="E3067" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="F3067" t="s">
         <v>18</v>
       </c>
       <c r="G3067" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3068" spans="1:7" x14ac:dyDescent="0.3">
@@ -72666,10 +72666,10 @@
         <v>199</v>
       </c>
       <c r="D3068" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="E3068" t="s">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="F3068" t="s">
         <v>18</v>
@@ -72689,13 +72689,13 @@
         <v>199</v>
       </c>
       <c r="D3069" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="E3069" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="F3069" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3069" t="s">
         <v>12</v>
@@ -72712,13 +72712,13 @@
         <v>199</v>
       </c>
       <c r="D3070" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="E3070" t="s">
-        <v>105</v>
+        <v>17</v>
       </c>
       <c r="F3070" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3070" t="s">
         <v>12</v>
@@ -72735,13 +72735,13 @@
         <v>199</v>
       </c>
       <c r="D3071" t="s">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="E3071" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="F3071" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3071" t="s">
         <v>12</v>
@@ -72758,10 +72758,10 @@
         <v>199</v>
       </c>
       <c r="D3072" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="E3072" t="s">
-        <v>206</v>
+        <v>179</v>
       </c>
       <c r="F3072" t="s">
         <v>11</v>
@@ -72781,10 +72781,10 @@
         <v>199</v>
       </c>
       <c r="D3073" t="s">
-        <v>144</v>
+        <v>182</v>
       </c>
       <c r="E3073" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
       <c r="F3073" t="s">
         <v>11</v>
@@ -72804,10 +72804,10 @@
         <v>199</v>
       </c>
       <c r="D3074" t="s">
-        <v>106</v>
+        <v>144</v>
       </c>
       <c r="E3074" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F3074" t="s">
         <v>11</v>
@@ -72827,10 +72827,10 @@
         <v>199</v>
       </c>
       <c r="D3075" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="E3075" t="s">
-        <v>207</v>
+        <v>146</v>
       </c>
       <c r="F3075" t="s">
         <v>11</v>
@@ -72850,10 +72850,10 @@
         <v>199</v>
       </c>
       <c r="D3076" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="E3076" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
       <c r="F3076" t="s">
         <v>11</v>
@@ -72873,10 +72873,10 @@
         <v>199</v>
       </c>
       <c r="D3077" t="s">
-        <v>182</v>
+        <v>98</v>
       </c>
       <c r="E3077" t="s">
-        <v>183</v>
+        <v>99</v>
       </c>
       <c r="F3077" t="s">
         <v>11</v>
@@ -72896,10 +72896,10 @@
         <v>199</v>
       </c>
       <c r="D3078" t="s">
-        <v>106</v>
+        <v>182</v>
       </c>
       <c r="E3078" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="F3078" t="s">
         <v>11</v>
@@ -72919,10 +72919,10 @@
         <v>199</v>
       </c>
       <c r="D3079" t="s">
-        <v>166</v>
+        <v>106</v>
       </c>
       <c r="E3079" t="s">
-        <v>167</v>
+        <v>107</v>
       </c>
       <c r="F3079" t="s">
         <v>11</v>
@@ -72942,10 +72942,10 @@
         <v>199</v>
       </c>
       <c r="D3080" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="E3080" t="s">
-        <v>22</v>
+        <v>167</v>
       </c>
       <c r="F3080" t="s">
         <v>11</v>
@@ -72965,10 +72965,10 @@
         <v>199</v>
       </c>
       <c r="D3081" t="s">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="E3081" t="s">
-        <v>101</v>
+        <v>22</v>
       </c>
       <c r="F3081" t="s">
         <v>11</v>
@@ -72988,10 +72988,10 @@
         <v>199</v>
       </c>
       <c r="D3082" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="E3082" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="F3082" t="s">
         <v>11</v>
@@ -73011,10 +73011,10 @@
         <v>199</v>
       </c>
       <c r="D3083" t="s">
-        <v>24</v>
+        <v>129</v>
       </c>
       <c r="E3083" t="s">
-        <v>25</v>
+        <v>130</v>
       </c>
       <c r="F3083" t="s">
         <v>11</v>
@@ -73034,10 +73034,10 @@
         <v>199</v>
       </c>
       <c r="D3084" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="E3084" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="F3084" t="s">
         <v>11</v>
@@ -73057,10 +73057,10 @@
         <v>199</v>
       </c>
       <c r="D3085" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E3085" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F3085" t="s">
         <v>11</v>
@@ -73080,10 +73080,10 @@
         <v>199</v>
       </c>
       <c r="D3086" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E3086" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F3086" t="s">
         <v>11</v>
@@ -73103,10 +73103,10 @@
         <v>199</v>
       </c>
       <c r="D3087" t="s">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="E3087" t="s">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="F3087" t="s">
         <v>11</v>
@@ -73126,10 +73126,10 @@
         <v>199</v>
       </c>
       <c r="D3088" t="s">
-        <v>194</v>
+        <v>98</v>
       </c>
       <c r="E3088" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F3088" t="s">
         <v>11</v>
@@ -73149,10 +73149,10 @@
         <v>199</v>
       </c>
       <c r="D3089" t="s">
-        <v>76</v>
+        <v>194</v>
       </c>
       <c r="E3089" t="s">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="F3089" t="s">
         <v>11</v>
@@ -73172,13 +73172,13 @@
         <v>199</v>
       </c>
       <c r="D3090" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="E3090" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="F3090" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3090" t="s">
         <v>12</v>
@@ -73195,10 +73195,10 @@
         <v>199</v>
       </c>
       <c r="D3091" t="s">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="E3091" t="s">
-        <v>111</v>
+        <v>20</v>
       </c>
       <c r="F3091" t="s">
         <v>18</v>
@@ -73218,10 +73218,10 @@
         <v>199</v>
       </c>
       <c r="D3092" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="E3092" t="s">
-        <v>22</v>
+        <v>111</v>
       </c>
       <c r="F3092" t="s">
         <v>18</v>
@@ -73241,10 +73241,10 @@
         <v>199</v>
       </c>
       <c r="D3093" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E3093" t="s">
-        <v>170</v>
+        <v>22</v>
       </c>
       <c r="F3093" t="s">
         <v>18</v>
@@ -73264,10 +73264,10 @@
         <v>199</v>
       </c>
       <c r="D3094" t="s">
-        <v>131</v>
+        <v>154</v>
       </c>
       <c r="E3094" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="F3094" t="s">
         <v>18</v>
@@ -73287,10 +73287,10 @@
         <v>199</v>
       </c>
       <c r="D3095" t="s">
-        <v>63</v>
+        <v>131</v>
       </c>
       <c r="E3095" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="F3095" t="s">
         <v>18</v>
@@ -73310,13 +73310,13 @@
         <v>199</v>
       </c>
       <c r="D3096" t="s">
-        <v>144</v>
+        <v>63</v>
       </c>
       <c r="E3096" t="s">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="F3096" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3096" t="s">
         <v>12</v>
@@ -73333,10 +73333,10 @@
         <v>199</v>
       </c>
       <c r="D3097" t="s">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="E3097" t="s">
-        <v>202</v>
+        <v>145</v>
       </c>
       <c r="F3097" t="s">
         <v>11</v>
@@ -73356,13 +73356,13 @@
         <v>199</v>
       </c>
       <c r="D3098" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="E3098" t="s">
-        <v>14</v>
+        <v>202</v>
       </c>
       <c r="F3098" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G3098" t="s">
         <v>12</v>
@@ -73379,13 +73379,13 @@
         <v>199</v>
       </c>
       <c r="D3099" t="s">
-        <v>164</v>
+        <v>13</v>
       </c>
       <c r="E3099" t="s">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="F3099" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="G3099" t="s">
         <v>12</v>
@@ -73405,7 +73405,7 @@
         <v>164</v>
       </c>
       <c r="E3100" t="s">
-        <v>165</v>
+        <v>203</v>
       </c>
       <c r="F3100" t="s">
         <v>11</v>
@@ -73425,10 +73425,10 @@
         <v>199</v>
       </c>
       <c r="D3101" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="E3101" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F3101" t="s">
         <v>11</v>
@@ -73448,10 +73448,10 @@
         <v>199</v>
       </c>
       <c r="D3102" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E3102" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F3102" t="s">
         <v>11</v>
@@ -73471,10 +73471,10 @@
         <v>199</v>
       </c>
       <c r="D3103" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E3103" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="F3103" t="s">
         <v>11</v>
@@ -73497,7 +73497,7 @@
         <v>171</v>
       </c>
       <c r="E3104" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="F3104" t="s">
         <v>11</v>
@@ -73517,10 +73517,10 @@
         <v>199</v>
       </c>
       <c r="D3105" t="s">
-        <v>110</v>
+        <v>171</v>
       </c>
       <c r="E3105" t="s">
-        <v>111</v>
+        <v>172</v>
       </c>
       <c r="F3105" t="s">
         <v>11</v>
@@ -73540,15 +73540,38 @@
         <v>199</v>
       </c>
       <c r="D3106" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3106" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3106" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3106" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3107" t="s">
+        <v>581</v>
+      </c>
+      <c r="B3107" t="s">
+        <v>285</v>
+      </c>
+      <c r="C3107" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3107" t="s">
         <v>200</v>
       </c>
-      <c r="E3106" t="s">
+      <c r="E3107" t="s">
         <v>201</v>
       </c>
-      <c r="F3106" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3106" t="s">
+      <c r="F3107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3107" t="s">
         <v>12</v>
       </c>
     </row>
